--- a/입시결과4.xlsx
+++ b/입시결과4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\02_Analysis\01_2024_Result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91309008-8BDE-4C8A-848B-D6AD07617DF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA2C7876-5444-4C51-A571-5C8B787D5AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-10365" windowWidth="16440" windowHeight="28320" xr2:uid="{5F448DE1-2C11-4C28-BE33-0B2F9FFA91F2}"/>
   </bookViews>
@@ -2373,9 +2373,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>동국대WISE</t>
-  </si>
-  <si>
     <t>단국대(죽전)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2477,6 +2474,10 @@
   </si>
   <si>
     <t>춘천교대</t>
+  </si>
+  <si>
+    <t>동국대(WISE)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2889,7 +2890,7 @@
         <v>9</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.4">
@@ -2927,7 +2928,7 @@
         <v>7</v>
       </c>
       <c r="L2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.4">
@@ -2965,7 +2966,7 @@
         <v>7</v>
       </c>
       <c r="L3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.4">
@@ -3003,7 +3004,7 @@
         <v>7</v>
       </c>
       <c r="L4" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
@@ -3041,7 +3042,7 @@
         <v>7</v>
       </c>
       <c r="L5" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.4">
@@ -3079,7 +3080,7 @@
         <v>7</v>
       </c>
       <c r="L6" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.4">
@@ -3117,7 +3118,7 @@
         <v>5</v>
       </c>
       <c r="L7" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.4">
@@ -3155,7 +3156,7 @@
         <v>5</v>
       </c>
       <c r="L8" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.4">
@@ -3193,7 +3194,7 @@
         <v>5</v>
       </c>
       <c r="L9" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.4">
@@ -3231,7 +3232,7 @@
         <v>5</v>
       </c>
       <c r="L10" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.4">
@@ -3269,7 +3270,7 @@
         <v>5</v>
       </c>
       <c r="L11" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.4">
@@ -3307,7 +3308,7 @@
         <v>8</v>
       </c>
       <c r="L12" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.4">
@@ -3345,7 +3346,7 @@
         <v>8</v>
       </c>
       <c r="L13" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.4">
@@ -3383,7 +3384,7 @@
         <v>5</v>
       </c>
       <c r="L14" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.4">
@@ -3421,7 +3422,7 @@
         <v>6</v>
       </c>
       <c r="L15" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.4">
@@ -3459,7 +3460,7 @@
         <v>7</v>
       </c>
       <c r="L16" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.4">
@@ -3495,7 +3496,7 @@
         <v>6</v>
       </c>
       <c r="L17" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.4">
@@ -3531,7 +3532,7 @@
         <v>6</v>
       </c>
       <c r="L18" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.4">
@@ -3567,7 +3568,7 @@
         <v>6</v>
       </c>
       <c r="L19" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.4">
@@ -3595,7 +3596,7 @@
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
       <c r="L20" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.4">
@@ -3623,7 +3624,7 @@
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
       <c r="L21" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.4">
@@ -3661,7 +3662,7 @@
         <v>3</v>
       </c>
       <c r="L22" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.4">
@@ -3669,7 +3670,7 @@
         <v>2022</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>241</v>
@@ -3699,7 +3700,7 @@
         <v>3</v>
       </c>
       <c r="L23" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.4">
@@ -3737,7 +3738,7 @@
         <v>3</v>
       </c>
       <c r="L24" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.4">
@@ -3775,7 +3776,7 @@
         <v>8</v>
       </c>
       <c r="L25" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.4">
@@ -3813,7 +3814,7 @@
         <v>5</v>
       </c>
       <c r="L26" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.4">
@@ -3851,7 +3852,7 @@
         <v>7</v>
       </c>
       <c r="L27" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.4">
@@ -3889,7 +3890,7 @@
         <v>7</v>
       </c>
       <c r="L28" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.4">
@@ -3927,7 +3928,7 @@
         <v>7</v>
       </c>
       <c r="L29" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.4">
@@ -3965,7 +3966,7 @@
         <v>7</v>
       </c>
       <c r="L30" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.4">
@@ -4003,7 +4004,7 @@
         <v>7</v>
       </c>
       <c r="L31" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.4">
@@ -4041,7 +4042,7 @@
         <v>7</v>
       </c>
       <c r="L32" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.4">
@@ -4079,7 +4080,7 @@
         <v>6</v>
       </c>
       <c r="L33" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.4">
@@ -4117,7 +4118,7 @@
         <v>6</v>
       </c>
       <c r="L34" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.4">
@@ -4145,7 +4146,7 @@
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
       <c r="L35" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.4">
@@ -4173,7 +4174,7 @@
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
       <c r="L36" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.4">
@@ -4211,7 +4212,7 @@
         <v>7</v>
       </c>
       <c r="L37" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.4">
@@ -4239,7 +4240,7 @@
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
       <c r="L38" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.4">
@@ -4277,7 +4278,7 @@
         <v>9</v>
       </c>
       <c r="L39" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.4">
@@ -4315,7 +4316,7 @@
         <v>6</v>
       </c>
       <c r="L40" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.4">
@@ -4353,7 +4354,7 @@
         <v>6</v>
       </c>
       <c r="L41" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.4">
@@ -4391,7 +4392,7 @@
         <v>3</v>
       </c>
       <c r="L42" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.4">
@@ -4429,7 +4430,7 @@
         <v>3</v>
       </c>
       <c r="L43" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.4">
@@ -4467,7 +4468,7 @@
         <v>3</v>
       </c>
       <c r="L44" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.4">
@@ -4505,7 +4506,7 @@
         <v>3</v>
       </c>
       <c r="L45" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.4">
@@ -4543,7 +4544,7 @@
         <v>3</v>
       </c>
       <c r="L46" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.4">
@@ -4581,7 +4582,7 @@
         <v>9</v>
       </c>
       <c r="L47" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.4">
@@ -4619,7 +4620,7 @@
         <v>9</v>
       </c>
       <c r="L48" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.4">
@@ -4657,7 +4658,7 @@
         <v>9</v>
       </c>
       <c r="L49" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.4">
@@ -4695,7 +4696,7 @@
         <v>9</v>
       </c>
       <c r="L50" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.4">
@@ -4733,7 +4734,7 @@
         <v>9</v>
       </c>
       <c r="L51" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.4">
@@ -4771,7 +4772,7 @@
         <v>9</v>
       </c>
       <c r="L52" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.4">
@@ -4809,7 +4810,7 @@
         <v>9</v>
       </c>
       <c r="L53" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.4">
@@ -4847,7 +4848,7 @@
         <v>6</v>
       </c>
       <c r="L54" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.4">
@@ -4885,7 +4886,7 @@
         <v>6</v>
       </c>
       <c r="L55" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.4">
@@ -4913,7 +4914,7 @@
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
       <c r="L56" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.4">
@@ -4941,7 +4942,7 @@
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
       <c r="L57" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.4">
@@ -4969,7 +4970,7 @@
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
       <c r="L58" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.4">
@@ -5007,7 +5008,7 @@
         <v>7</v>
       </c>
       <c r="L59" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.4">
@@ -5045,7 +5046,7 @@
         <v>7</v>
       </c>
       <c r="L60" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.4">
@@ -5083,7 +5084,7 @@
         <v>7</v>
       </c>
       <c r="L61" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.4">
@@ -5121,7 +5122,7 @@
         <v>6</v>
       </c>
       <c r="L62" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.4">
@@ -5159,7 +5160,7 @@
         <v>7</v>
       </c>
       <c r="L63" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.4">
@@ -5197,7 +5198,7 @@
         <v>7</v>
       </c>
       <c r="L64" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.4">
@@ -5235,7 +5236,7 @@
         <v>7</v>
       </c>
       <c r="L65" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.4">
@@ -5273,7 +5274,7 @@
         <v>7</v>
       </c>
       <c r="L66" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.4">
@@ -5311,7 +5312,7 @@
         <v>7</v>
       </c>
       <c r="L67" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.4">
@@ -5349,7 +5350,7 @@
         <v>8</v>
       </c>
       <c r="L68" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.4">
@@ -5387,7 +5388,7 @@
         <v>8</v>
       </c>
       <c r="L69" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.4">
@@ -5425,7 +5426,7 @@
         <v>8</v>
       </c>
       <c r="L70" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.4">
@@ -5463,7 +5464,7 @@
         <v>8</v>
       </c>
       <c r="L71" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.4">
@@ -5501,7 +5502,7 @@
         <v>8</v>
       </c>
       <c r="L72" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.4">
@@ -5539,7 +5540,7 @@
         <v>9</v>
       </c>
       <c r="L73" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.4">
@@ -5577,7 +5578,7 @@
         <v>9</v>
       </c>
       <c r="L74" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.4">
@@ -5615,7 +5616,7 @@
         <v>6</v>
       </c>
       <c r="L75" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.4">
@@ -5653,7 +5654,7 @@
         <v>5</v>
       </c>
       <c r="L76" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.4">
@@ -5691,7 +5692,7 @@
         <v>5</v>
       </c>
       <c r="L77" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.4">
@@ -5729,7 +5730,7 @@
         <v>5</v>
       </c>
       <c r="L78" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.4">
@@ -5767,7 +5768,7 @@
         <v>5</v>
       </c>
       <c r="L79" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.4">
@@ -5805,7 +5806,7 @@
         <v>7</v>
       </c>
       <c r="L80" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.4">
@@ -5843,7 +5844,7 @@
         <v>8</v>
       </c>
       <c r="L81" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.4">
@@ -5881,7 +5882,7 @@
         <v>8</v>
       </c>
       <c r="L82" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.4">
@@ -5919,7 +5920,7 @@
         <v>8</v>
       </c>
       <c r="L83" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.4">
@@ -5947,7 +5948,7 @@
       <c r="J84" s="2"/>
       <c r="K84" s="2"/>
       <c r="L84" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.4">
@@ -5985,7 +5986,7 @@
         <v>7</v>
       </c>
       <c r="L85" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.4">
@@ -6023,7 +6024,7 @@
         <v>7</v>
       </c>
       <c r="L86" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.4">
@@ -6061,7 +6062,7 @@
         <v>7</v>
       </c>
       <c r="L87" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.4">
@@ -6099,7 +6100,7 @@
         <v>7</v>
       </c>
       <c r="L88" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.4">
@@ -6137,7 +6138,7 @@
         <v>7</v>
       </c>
       <c r="L89" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.4">
@@ -6175,7 +6176,7 @@
         <v>7</v>
       </c>
       <c r="L90" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.4">
@@ -6213,7 +6214,7 @@
         <v>7</v>
       </c>
       <c r="L91" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.4">
@@ -6251,7 +6252,7 @@
         <v>7</v>
       </c>
       <c r="L92" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.4">
@@ -6289,7 +6290,7 @@
         <v>7</v>
       </c>
       <c r="L93" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.4">
@@ -6317,7 +6318,7 @@
       <c r="J94" s="2"/>
       <c r="K94" s="2"/>
       <c r="L94" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.4">
@@ -6345,7 +6346,7 @@
       <c r="J95" s="2"/>
       <c r="K95" s="2"/>
       <c r="L95" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.4">
@@ -6383,7 +6384,7 @@
         <v>7</v>
       </c>
       <c r="L96" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.4">
@@ -6421,7 +6422,7 @@
         <v>6</v>
       </c>
       <c r="L97" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.4">
@@ -6459,7 +6460,7 @@
         <v>6</v>
       </c>
       <c r="L98" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.4">
@@ -6497,7 +6498,7 @@
         <v>6</v>
       </c>
       <c r="L99" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.4">
@@ -6535,7 +6536,7 @@
         <v>7</v>
       </c>
       <c r="L100" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.4">
@@ -6573,7 +6574,7 @@
         <v>9</v>
       </c>
       <c r="L101" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.4">
@@ -6611,7 +6612,7 @@
         <v>9</v>
       </c>
       <c r="L102" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.4">
@@ -6649,7 +6650,7 @@
         <v>9</v>
       </c>
       <c r="L103" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.4">
@@ -6687,7 +6688,7 @@
         <v>9</v>
       </c>
       <c r="L104" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.4">
@@ -6725,7 +6726,7 @@
         <v>9</v>
       </c>
       <c r="L105" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.4">
@@ -6763,7 +6764,7 @@
         <v>9</v>
       </c>
       <c r="L106" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.4">
@@ -6801,7 +6802,7 @@
         <v>9</v>
       </c>
       <c r="L107" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.4">
@@ -6839,7 +6840,7 @@
         <v>9</v>
       </c>
       <c r="L108" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.4">
@@ -6877,7 +6878,7 @@
         <v>7</v>
       </c>
       <c r="L109" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.4">
@@ -6915,7 +6916,7 @@
         <v>7</v>
       </c>
       <c r="L110" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.4">
@@ -6953,7 +6954,7 @@
         <v>6</v>
       </c>
       <c r="L111" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.4">
@@ -6991,7 +6992,7 @@
         <v>6</v>
       </c>
       <c r="L112" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.4">
@@ -7029,7 +7030,7 @@
         <v>6</v>
       </c>
       <c r="L113" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.4">
@@ -7067,7 +7068,7 @@
         <v>6</v>
       </c>
       <c r="L114" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.4">
@@ -7105,7 +7106,7 @@
         <v>6</v>
       </c>
       <c r="L115" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.4">
@@ -7143,7 +7144,7 @@
         <v>1</v>
       </c>
       <c r="L116" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.4">
@@ -7181,7 +7182,7 @@
         <v>1</v>
       </c>
       <c r="L117" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.4">
@@ -7219,7 +7220,7 @@
         <v>1</v>
       </c>
       <c r="L118" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.4">
@@ -7257,7 +7258,7 @@
         <v>1</v>
       </c>
       <c r="L119" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.4">
@@ -7295,7 +7296,7 @@
         <v>1</v>
       </c>
       <c r="L120" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.4">
@@ -7333,7 +7334,7 @@
         <v>4</v>
       </c>
       <c r="L121" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.4">
@@ -7371,7 +7372,7 @@
         <v>6</v>
       </c>
       <c r="L122" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.4">
@@ -7409,7 +7410,7 @@
         <v>6</v>
       </c>
       <c r="L123" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.4">
@@ -7447,7 +7448,7 @@
         <v>3</v>
       </c>
       <c r="L124" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.4">
@@ -7485,7 +7486,7 @@
         <v>4</v>
       </c>
       <c r="L125" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.4">
@@ -7523,7 +7524,7 @@
         <v>2</v>
       </c>
       <c r="L126" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.4">
@@ -7561,7 +7562,7 @@
         <v>6</v>
       </c>
       <c r="L127" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.4">
@@ -7569,7 +7570,7 @@
         <v>2022</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>62</v>
@@ -7599,7 +7600,7 @@
         <v>4</v>
       </c>
       <c r="L128" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.4">
@@ -7637,7 +7638,7 @@
         <v>8</v>
       </c>
       <c r="L129" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.4">
@@ -7675,7 +7676,7 @@
         <v>6</v>
       </c>
       <c r="L130" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.4">
@@ -7713,7 +7714,7 @@
         <v>6</v>
       </c>
       <c r="L131" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.4">
@@ -7751,7 +7752,7 @@
         <v>6</v>
       </c>
       <c r="L132" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.4">
@@ -7789,7 +7790,7 @@
         <v>5</v>
       </c>
       <c r="L133" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.4">
@@ -7827,7 +7828,7 @@
         <v>5</v>
       </c>
       <c r="L134" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.4">
@@ -7865,7 +7866,7 @@
         <v>5</v>
       </c>
       <c r="L135" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.4">
@@ -7903,7 +7904,7 @@
         <v>5</v>
       </c>
       <c r="L136" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.4">
@@ -7931,7 +7932,7 @@
       <c r="J137" s="2"/>
       <c r="K137" s="2"/>
       <c r="L137" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.4">
@@ -7959,7 +7960,7 @@
       <c r="J138" s="2"/>
       <c r="K138" s="2"/>
       <c r="L138" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.4">
@@ -7997,7 +7998,7 @@
         <v>7</v>
       </c>
       <c r="L139" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.4">
@@ -8035,7 +8036,7 @@
         <v>7</v>
       </c>
       <c r="L140" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.4">
@@ -8073,7 +8074,7 @@
         <v>6</v>
       </c>
       <c r="L141" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.4">
@@ -8111,7 +8112,7 @@
         <v>6</v>
       </c>
       <c r="L142" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.4">
@@ -8149,7 +8150,7 @@
         <v>6</v>
       </c>
       <c r="L143" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.4">
@@ -8187,7 +8188,7 @@
         <v>5</v>
       </c>
       <c r="L144" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.4">
@@ -8225,7 +8226,7 @@
         <v>5</v>
       </c>
       <c r="L145" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.4">
@@ -8263,7 +8264,7 @@
         <v>5</v>
       </c>
       <c r="L146" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.4">
@@ -8301,7 +8302,7 @@
         <v>5</v>
       </c>
       <c r="L147" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.4">
@@ -8339,7 +8340,7 @@
         <v>8</v>
       </c>
       <c r="L148" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.4">
@@ -8377,7 +8378,7 @@
         <v>9</v>
       </c>
       <c r="L149" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.4">
@@ -8415,7 +8416,7 @@
         <v>9</v>
       </c>
       <c r="L150" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.4">
@@ -8453,7 +8454,7 @@
         <v>9</v>
       </c>
       <c r="L151" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.4">
@@ -8491,7 +8492,7 @@
         <v>9</v>
       </c>
       <c r="L152" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.4">
@@ -8529,7 +8530,7 @@
         <v>9</v>
       </c>
       <c r="L153" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.4">
@@ -8567,7 +8568,7 @@
         <v>7</v>
       </c>
       <c r="L154" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.4">
@@ -8605,7 +8606,7 @@
         <v>7</v>
       </c>
       <c r="L155" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.4">
@@ -8643,7 +8644,7 @@
         <v>5</v>
       </c>
       <c r="L156" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.4">
@@ -8681,7 +8682,7 @@
         <v>5</v>
       </c>
       <c r="L157" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.4">
@@ -8719,7 +8720,7 @@
         <v>8</v>
       </c>
       <c r="L158" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.4">
@@ -8757,7 +8758,7 @@
         <v>8</v>
       </c>
       <c r="L159" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.4">
@@ -8795,7 +8796,7 @@
         <v>8</v>
       </c>
       <c r="L160" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.4">
@@ -8833,7 +8834,7 @@
         <v>8</v>
       </c>
       <c r="L161" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.4">
@@ -8871,7 +8872,7 @@
         <v>8</v>
       </c>
       <c r="L162" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.4">
@@ -8909,7 +8910,7 @@
         <v>6</v>
       </c>
       <c r="L163" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.4">
@@ -8947,7 +8948,7 @@
         <v>7</v>
       </c>
       <c r="L164" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.4">
@@ -8985,7 +8986,7 @@
         <v>7</v>
       </c>
       <c r="L165" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.4">
@@ -9023,7 +9024,7 @@
         <v>7</v>
       </c>
       <c r="L166" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.4">
@@ -9061,7 +9062,7 @@
         <v>7</v>
       </c>
       <c r="L167" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.4">
@@ -9099,7 +9100,7 @@
         <v>7</v>
       </c>
       <c r="L168" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.4">
@@ -9137,7 +9138,7 @@
         <v>7</v>
       </c>
       <c r="L169" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.4">
@@ -9175,7 +9176,7 @@
         <v>7</v>
       </c>
       <c r="L170" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.4">
@@ -9213,7 +9214,7 @@
         <v>7</v>
       </c>
       <c r="L171" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.4">
@@ -9251,7 +9252,7 @@
         <v>7</v>
       </c>
       <c r="L172" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.4">
@@ -9289,7 +9290,7 @@
         <v>6</v>
       </c>
       <c r="L173" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.4">
@@ -9327,7 +9328,7 @@
         <v>6</v>
       </c>
       <c r="L174" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.4">
@@ -9365,7 +9366,7 @@
         <v>6</v>
       </c>
       <c r="L175" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.4">
@@ -9403,7 +9404,7 @@
         <v>6</v>
       </c>
       <c r="L176" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.4">
@@ -9441,7 +9442,7 @@
         <v>2</v>
       </c>
       <c r="L177" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.4">
@@ -9479,7 +9480,7 @@
         <v>3</v>
       </c>
       <c r="L178" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.4">
@@ -9517,7 +9518,7 @@
         <v>3</v>
       </c>
       <c r="L179" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.4">
@@ -9555,7 +9556,7 @@
         <v>3</v>
       </c>
       <c r="L180" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.4">
@@ -9593,7 +9594,7 @@
         <v>8</v>
       </c>
       <c r="L181" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.4">
@@ -9631,7 +9632,7 @@
         <v>8</v>
       </c>
       <c r="L182" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.4">
@@ -9659,7 +9660,7 @@
       <c r="J183" s="2"/>
       <c r="K183" s="2"/>
       <c r="L183" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.4">
@@ -9687,7 +9688,7 @@
       <c r="J184" s="2"/>
       <c r="K184" s="2"/>
       <c r="L184" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.4">
@@ -9725,7 +9726,7 @@
         <v>5</v>
       </c>
       <c r="L185" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.4">
@@ -9763,7 +9764,7 @@
         <v>2</v>
       </c>
       <c r="L186" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.4">
@@ -9801,7 +9802,7 @@
         <v>2</v>
       </c>
       <c r="L187" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.4">
@@ -9839,7 +9840,7 @@
         <v>4</v>
       </c>
       <c r="L188" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.4">
@@ -9867,7 +9868,7 @@
       <c r="J189" s="2"/>
       <c r="K189" s="2"/>
       <c r="L189" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.4">
@@ -9905,7 +9906,7 @@
         <v>6</v>
       </c>
       <c r="L190" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.4">
@@ -9943,7 +9944,7 @@
         <v>8</v>
       </c>
       <c r="L191" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.4">
@@ -9981,7 +9982,7 @@
         <v>7</v>
       </c>
       <c r="L192" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.4">
@@ -10019,7 +10020,7 @@
         <v>7</v>
       </c>
       <c r="L193" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.4">
@@ -10057,7 +10058,7 @@
         <v>9</v>
       </c>
       <c r="L194" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.4">
@@ -10095,7 +10096,7 @@
         <v>4</v>
       </c>
       <c r="L195" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.4">
@@ -10133,7 +10134,7 @@
         <v>5</v>
       </c>
       <c r="L196" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.4">
@@ -10171,7 +10172,7 @@
         <v>7</v>
       </c>
       <c r="L197" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.4">
@@ -10209,7 +10210,7 @@
         <v>7</v>
       </c>
       <c r="L198" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.4">
@@ -10247,7 +10248,7 @@
         <v>4</v>
       </c>
       <c r="L199" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.4">
@@ -10285,7 +10286,7 @@
         <v>4</v>
       </c>
       <c r="L200" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.4">
@@ -10323,7 +10324,7 @@
         <v>5</v>
       </c>
       <c r="L201" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.4">
@@ -10361,7 +10362,7 @@
         <v>7</v>
       </c>
       <c r="L202" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.4">
@@ -10399,7 +10400,7 @@
         <v>7</v>
       </c>
       <c r="L203" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.4">
@@ -10437,7 +10438,7 @@
         <v>4</v>
       </c>
       <c r="L204" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.4">
@@ -10475,7 +10476,7 @@
         <v>4</v>
       </c>
       <c r="L205" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.4">
@@ -10513,7 +10514,7 @@
         <v>4</v>
       </c>
       <c r="L206" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.4">
@@ -10541,7 +10542,7 @@
       <c r="J207" s="2"/>
       <c r="K207" s="2"/>
       <c r="L207" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.4">
@@ -10569,7 +10570,7 @@
       <c r="J208" s="1"/>
       <c r="K208" s="1"/>
       <c r="L208" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.4">
@@ -10597,7 +10598,7 @@
       <c r="J209" s="1"/>
       <c r="K209" s="1"/>
       <c r="L209" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.4">
@@ -10635,7 +10636,7 @@
         <v>7</v>
       </c>
       <c r="L210" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.4">
@@ -10673,7 +10674,7 @@
         <v>9</v>
       </c>
       <c r="L211" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.4">
@@ -10711,7 +10712,7 @@
         <v>9</v>
       </c>
       <c r="L212" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.4">
@@ -10749,7 +10750,7 @@
         <v>5</v>
       </c>
       <c r="L213" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.4">
@@ -10787,7 +10788,7 @@
         <v>5</v>
       </c>
       <c r="L214" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.4">
@@ -10815,7 +10816,7 @@
       <c r="J215" s="2"/>
       <c r="K215" s="2"/>
       <c r="L215" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.4">
@@ -10843,7 +10844,7 @@
       <c r="J216" s="2"/>
       <c r="K216" s="2"/>
       <c r="L216" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.4">
@@ -10871,7 +10872,7 @@
       <c r="J217" s="2"/>
       <c r="K217" s="2"/>
       <c r="L217" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.4">
@@ -10899,7 +10900,7 @@
       <c r="J218" s="2"/>
       <c r="K218" s="2"/>
       <c r="L218" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.4">
@@ -10927,7 +10928,7 @@
       <c r="J219" s="2"/>
       <c r="K219" s="2"/>
       <c r="L219" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.4">
@@ -10965,7 +10966,7 @@
         <v>8</v>
       </c>
       <c r="L220" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.4">
@@ -11003,7 +11004,7 @@
         <v>8</v>
       </c>
       <c r="L221" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="222" spans="1:12" x14ac:dyDescent="0.4">
@@ -11041,7 +11042,7 @@
         <v>8</v>
       </c>
       <c r="L222" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.4">
@@ -11079,7 +11080,7 @@
         <v>8</v>
       </c>
       <c r="L223" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="224" spans="1:12" x14ac:dyDescent="0.4">
@@ -11117,7 +11118,7 @@
         <v>5</v>
       </c>
       <c r="L224" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="225" spans="1:12" x14ac:dyDescent="0.4">
@@ -11155,7 +11156,7 @@
         <v>3</v>
       </c>
       <c r="L225" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="226" spans="1:12" x14ac:dyDescent="0.4">
@@ -11193,7 +11194,7 @@
         <v>3</v>
       </c>
       <c r="L226" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.4">
@@ -11231,7 +11232,7 @@
         <v>3</v>
       </c>
       <c r="L227" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.4">
@@ -11269,7 +11270,7 @@
         <v>3</v>
       </c>
       <c r="L228" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.4">
@@ -11307,7 +11308,7 @@
         <v>6</v>
       </c>
       <c r="L229" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.4">
@@ -11345,7 +11346,7 @@
         <v>6</v>
       </c>
       <c r="L230" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.4">
@@ -11383,7 +11384,7 @@
         <v>7</v>
       </c>
       <c r="L231" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.4">
@@ -11421,7 +11422,7 @@
         <v>6</v>
       </c>
       <c r="L232" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.4">
@@ -11459,7 +11460,7 @@
         <v>8</v>
       </c>
       <c r="L233" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.4">
@@ -11497,7 +11498,7 @@
         <v>8</v>
       </c>
       <c r="L234" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.4">
@@ -11535,7 +11536,7 @@
         <v>8</v>
       </c>
       <c r="L235" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.4">
@@ -11573,7 +11574,7 @@
         <v>5</v>
       </c>
       <c r="L236" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.4">
@@ -11581,7 +11582,7 @@
         <v>2023</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>241</v>
@@ -11611,7 +11612,7 @@
         <v>5</v>
       </c>
       <c r="L237" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="238" spans="1:12" x14ac:dyDescent="0.4">
@@ -11649,7 +11650,7 @@
         <v>5</v>
       </c>
       <c r="L238" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="239" spans="1:12" x14ac:dyDescent="0.4">
@@ -11687,7 +11688,7 @@
         <v>5</v>
       </c>
       <c r="L239" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.4">
@@ -11725,7 +11726,7 @@
         <v>9</v>
       </c>
       <c r="L240" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="241" spans="1:12" x14ac:dyDescent="0.4">
@@ -11763,7 +11764,7 @@
         <v>9</v>
       </c>
       <c r="L241" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="242" spans="1:12" x14ac:dyDescent="0.4">
@@ -11801,7 +11802,7 @@
         <v>9</v>
       </c>
       <c r="L242" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="243" spans="1:12" x14ac:dyDescent="0.4">
@@ -11839,7 +11840,7 @@
         <v>7</v>
       </c>
       <c r="L243" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="244" spans="1:12" x14ac:dyDescent="0.4">
@@ -11877,7 +11878,7 @@
         <v>7</v>
       </c>
       <c r="L244" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="245" spans="1:12" x14ac:dyDescent="0.4">
@@ -11905,7 +11906,7 @@
       <c r="J245" s="2"/>
       <c r="K245" s="2"/>
       <c r="L245" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.4">
@@ -11933,7 +11934,7 @@
       <c r="J246" s="1"/>
       <c r="K246" s="1"/>
       <c r="L246" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="247" spans="1:12" x14ac:dyDescent="0.4">
@@ -11971,7 +11972,7 @@
         <v>7</v>
       </c>
       <c r="L247" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.4">
@@ -12009,7 +12010,7 @@
         <v>7</v>
       </c>
       <c r="L248" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="249" spans="1:12" x14ac:dyDescent="0.4">
@@ -12047,7 +12048,7 @@
         <v>6</v>
       </c>
       <c r="L249" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.4">
@@ -12085,7 +12086,7 @@
         <v>6</v>
       </c>
       <c r="L250" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.4">
@@ -12093,7 +12094,7 @@
         <v>2023</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>83</v>
@@ -12123,7 +12124,7 @@
         <v>6</v>
       </c>
       <c r="L251" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.4">
@@ -12161,7 +12162,7 @@
         <v>6</v>
       </c>
       <c r="L252" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.4">
@@ -12199,7 +12200,7 @@
         <v>6</v>
       </c>
       <c r="L253" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.4">
@@ -12237,7 +12238,7 @@
         <v>6</v>
       </c>
       <c r="L254" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.4">
@@ -12275,7 +12276,7 @@
         <v>6</v>
       </c>
       <c r="L255" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="256" spans="1:12" x14ac:dyDescent="0.4">
@@ -12313,7 +12314,7 @@
         <v>6</v>
       </c>
       <c r="L256" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.4">
@@ -12351,7 +12352,7 @@
         <v>6</v>
       </c>
       <c r="L257" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.4">
@@ -12379,7 +12380,7 @@
       <c r="J258" s="2"/>
       <c r="K258" s="2"/>
       <c r="L258" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.4">
@@ -12407,7 +12408,7 @@
       <c r="J259" s="2"/>
       <c r="K259" s="2"/>
       <c r="L259" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.4">
@@ -12435,7 +12436,7 @@
       <c r="J260" s="2"/>
       <c r="K260" s="2"/>
       <c r="L260" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.4">
@@ -12473,7 +12474,7 @@
         <v>7</v>
       </c>
       <c r="L261" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.4">
@@ -12511,7 +12512,7 @@
         <v>7</v>
       </c>
       <c r="L262" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.4">
@@ -12549,7 +12550,7 @@
         <v>5</v>
       </c>
       <c r="L263" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.4">
@@ -12587,7 +12588,7 @@
         <v>6</v>
       </c>
       <c r="L264" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.4">
@@ -12625,7 +12626,7 @@
         <v>6</v>
       </c>
       <c r="L265" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.4">
@@ -12663,7 +12664,7 @@
         <v>4</v>
       </c>
       <c r="L266" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.4">
@@ -12701,7 +12702,7 @@
         <v>4</v>
       </c>
       <c r="L267" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.4">
@@ -12739,7 +12740,7 @@
         <v>4</v>
       </c>
       <c r="L268" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.4">
@@ -12777,7 +12778,7 @@
         <v>7</v>
       </c>
       <c r="L269" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.4">
@@ -12815,7 +12816,7 @@
         <v>7</v>
       </c>
       <c r="L270" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.4">
@@ -12853,7 +12854,7 @@
         <v>6</v>
       </c>
       <c r="L271" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.4">
@@ -12891,7 +12892,7 @@
         <v>6</v>
       </c>
       <c r="L272" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="273" spans="1:12" x14ac:dyDescent="0.4">
@@ -12929,7 +12930,7 @@
         <v>5</v>
       </c>
       <c r="L273" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="274" spans="1:12" x14ac:dyDescent="0.4">
@@ -12967,7 +12968,7 @@
         <v>5</v>
       </c>
       <c r="L274" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="275" spans="1:12" x14ac:dyDescent="0.4">
@@ -13005,7 +13006,7 @@
         <v>5</v>
       </c>
       <c r="L275" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="276" spans="1:12" x14ac:dyDescent="0.4">
@@ -13043,7 +13044,7 @@
         <v>6</v>
       </c>
       <c r="L276" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="277" spans="1:12" x14ac:dyDescent="0.4">
@@ -13081,7 +13082,7 @@
         <v>6</v>
       </c>
       <c r="L277" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="278" spans="1:12" x14ac:dyDescent="0.4">
@@ -13119,7 +13120,7 @@
         <v>6</v>
       </c>
       <c r="L278" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="279" spans="1:12" x14ac:dyDescent="0.4">
@@ -13157,7 +13158,7 @@
         <v>6</v>
       </c>
       <c r="L279" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="280" spans="1:12" x14ac:dyDescent="0.4">
@@ -13195,7 +13196,7 @@
         <v>6</v>
       </c>
       <c r="L280" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="281" spans="1:12" x14ac:dyDescent="0.4">
@@ -13233,7 +13234,7 @@
         <v>4</v>
       </c>
       <c r="L281" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="282" spans="1:12" x14ac:dyDescent="0.4">
@@ -13271,7 +13272,7 @@
         <v>4</v>
       </c>
       <c r="L282" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="283" spans="1:12" x14ac:dyDescent="0.4">
@@ -13309,7 +13310,7 @@
         <v>4</v>
       </c>
       <c r="L283" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="284" spans="1:12" x14ac:dyDescent="0.4">
@@ -13347,7 +13348,7 @@
         <v>6</v>
       </c>
       <c r="L284" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="285" spans="1:12" x14ac:dyDescent="0.4">
@@ -13385,7 +13386,7 @@
         <v>5</v>
       </c>
       <c r="L285" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="286" spans="1:12" x14ac:dyDescent="0.4">
@@ -13423,7 +13424,7 @@
         <v>5</v>
       </c>
       <c r="L286" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="287" spans="1:12" x14ac:dyDescent="0.4">
@@ -13461,7 +13462,7 @@
         <v>7</v>
       </c>
       <c r="L287" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="288" spans="1:12" x14ac:dyDescent="0.4">
@@ -13499,7 +13500,7 @@
         <v>7</v>
       </c>
       <c r="L288" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="289" spans="1:12" x14ac:dyDescent="0.4">
@@ -13537,7 +13538,7 @@
         <v>6</v>
       </c>
       <c r="L289" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="290" spans="1:12" x14ac:dyDescent="0.4">
@@ -13575,7 +13576,7 @@
         <v>6</v>
       </c>
       <c r="L290" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="291" spans="1:12" x14ac:dyDescent="0.4">
@@ -13613,7 +13614,7 @@
         <v>4</v>
       </c>
       <c r="L291" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="292" spans="1:12" x14ac:dyDescent="0.4">
@@ -13651,7 +13652,7 @@
         <v>8</v>
       </c>
       <c r="L292" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="293" spans="1:12" x14ac:dyDescent="0.4">
@@ -13689,7 +13690,7 @@
         <v>7</v>
       </c>
       <c r="L293" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="294" spans="1:12" x14ac:dyDescent="0.4">
@@ -13727,7 +13728,7 @@
         <v>7</v>
       </c>
       <c r="L294" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="295" spans="1:12" x14ac:dyDescent="0.4">
@@ -13765,7 +13766,7 @@
         <v>7</v>
       </c>
       <c r="L295" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="296" spans="1:12" x14ac:dyDescent="0.4">
@@ -13803,7 +13804,7 @@
         <v>7</v>
       </c>
       <c r="L296" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="297" spans="1:12" x14ac:dyDescent="0.4">
@@ -13841,7 +13842,7 @@
         <v>8</v>
       </c>
       <c r="L297" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="298" spans="1:12" x14ac:dyDescent="0.4">
@@ -13879,7 +13880,7 @@
         <v>6</v>
       </c>
       <c r="L298" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="299" spans="1:12" x14ac:dyDescent="0.4">
@@ -13917,7 +13918,7 @@
         <v>6</v>
       </c>
       <c r="L299" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="300" spans="1:12" x14ac:dyDescent="0.4">
@@ -13955,7 +13956,7 @@
         <v>7</v>
       </c>
       <c r="L300" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="301" spans="1:12" x14ac:dyDescent="0.4">
@@ -13993,7 +13994,7 @@
         <v>7</v>
       </c>
       <c r="L301" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="302" spans="1:12" x14ac:dyDescent="0.4">
@@ -14031,7 +14032,7 @@
         <v>7</v>
       </c>
       <c r="L302" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="303" spans="1:12" x14ac:dyDescent="0.4">
@@ -14069,7 +14070,7 @@
         <v>7</v>
       </c>
       <c r="L303" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="304" spans="1:12" x14ac:dyDescent="0.4">
@@ -14107,7 +14108,7 @@
         <v>7</v>
       </c>
       <c r="L304" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="305" spans="1:12" x14ac:dyDescent="0.4">
@@ -14145,7 +14146,7 @@
         <v>7</v>
       </c>
       <c r="L305" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="306" spans="1:12" x14ac:dyDescent="0.4">
@@ -14183,7 +14184,7 @@
         <v>7</v>
       </c>
       <c r="L306" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="307" spans="1:12" x14ac:dyDescent="0.4">
@@ -14221,7 +14222,7 @@
         <v>7</v>
       </c>
       <c r="L307" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="308" spans="1:12" x14ac:dyDescent="0.4">
@@ -14259,7 +14260,7 @@
         <v>8</v>
       </c>
       <c r="L308" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="309" spans="1:12" x14ac:dyDescent="0.4">
@@ -14293,7 +14294,7 @@
         <v>8</v>
       </c>
       <c r="L309" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="310" spans="1:12" x14ac:dyDescent="0.4">
@@ -14327,7 +14328,7 @@
         <v>8</v>
       </c>
       <c r="L310" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="311" spans="1:12" x14ac:dyDescent="0.4">
@@ -14361,7 +14362,7 @@
         <v>8</v>
       </c>
       <c r="L311" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="312" spans="1:12" x14ac:dyDescent="0.4">
@@ -14399,7 +14400,7 @@
         <v>6</v>
       </c>
       <c r="L312" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="313" spans="1:12" x14ac:dyDescent="0.4">
@@ -14437,7 +14438,7 @@
         <v>7</v>
       </c>
       <c r="L313" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="314" spans="1:12" x14ac:dyDescent="0.4">
@@ -14475,7 +14476,7 @@
         <v>4</v>
       </c>
       <c r="L314" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="315" spans="1:12" x14ac:dyDescent="0.4">
@@ -14511,7 +14512,7 @@
         <v>5</v>
       </c>
       <c r="L315" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="316" spans="1:12" x14ac:dyDescent="0.4">
@@ -14547,7 +14548,7 @@
         <v>5</v>
       </c>
       <c r="L316" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="317" spans="1:12" x14ac:dyDescent="0.4">
@@ -14585,7 +14586,7 @@
         <v>5</v>
       </c>
       <c r="L317" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="318" spans="1:12" x14ac:dyDescent="0.4">
@@ -14623,7 +14624,7 @@
         <v>8</v>
       </c>
       <c r="L318" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="319" spans="1:12" x14ac:dyDescent="0.4">
@@ -14661,7 +14662,7 @@
         <v>8</v>
       </c>
       <c r="L319" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="320" spans="1:12" x14ac:dyDescent="0.4">
@@ -14699,7 +14700,7 @@
         <v>5</v>
       </c>
       <c r="L320" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="321" spans="1:12" x14ac:dyDescent="0.4">
@@ -14737,7 +14738,7 @@
         <v>5</v>
       </c>
       <c r="L321" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="322" spans="1:12" x14ac:dyDescent="0.4">
@@ -14775,7 +14776,7 @@
         <v>1</v>
       </c>
       <c r="L322" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="323" spans="1:12" x14ac:dyDescent="0.4">
@@ -14813,7 +14814,7 @@
         <v>1</v>
       </c>
       <c r="L323" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="324" spans="1:12" x14ac:dyDescent="0.4">
@@ -14851,7 +14852,7 @@
         <v>1</v>
       </c>
       <c r="L324" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="325" spans="1:12" x14ac:dyDescent="0.4">
@@ -14889,7 +14890,7 @@
         <v>1</v>
       </c>
       <c r="L325" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="326" spans="1:12" x14ac:dyDescent="0.4">
@@ -14927,7 +14928,7 @@
         <v>5</v>
       </c>
       <c r="L326" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="327" spans="1:12" x14ac:dyDescent="0.4">
@@ -14965,7 +14966,7 @@
         <v>8</v>
       </c>
       <c r="L327" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="328" spans="1:12" x14ac:dyDescent="0.4">
@@ -15003,7 +15004,7 @@
         <v>8</v>
       </c>
       <c r="L328" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="329" spans="1:12" x14ac:dyDescent="0.4">
@@ -15041,7 +15042,7 @@
         <v>4</v>
       </c>
       <c r="L329" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="330" spans="1:12" x14ac:dyDescent="0.4">
@@ -15079,7 +15080,7 @@
         <v>4</v>
       </c>
       <c r="L330" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="331" spans="1:12" x14ac:dyDescent="0.4">
@@ -15117,7 +15118,7 @@
         <v>8</v>
       </c>
       <c r="L331" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="332" spans="1:12" x14ac:dyDescent="0.4">
@@ -15155,7 +15156,7 @@
         <v>6</v>
       </c>
       <c r="L332" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="333" spans="1:12" x14ac:dyDescent="0.4">
@@ -15193,7 +15194,7 @@
         <v>6</v>
       </c>
       <c r="L333" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="334" spans="1:12" x14ac:dyDescent="0.4">
@@ -15231,7 +15232,7 @@
         <v>6</v>
       </c>
       <c r="L334" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="335" spans="1:12" x14ac:dyDescent="0.4">
@@ -15269,7 +15270,7 @@
         <v>7</v>
       </c>
       <c r="L335" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="336" spans="1:12" x14ac:dyDescent="0.4">
@@ -15307,7 +15308,7 @@
         <v>7</v>
       </c>
       <c r="L336" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="337" spans="1:12" x14ac:dyDescent="0.4">
@@ -15345,7 +15346,7 @@
         <v>8</v>
       </c>
       <c r="L337" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="338" spans="1:12" x14ac:dyDescent="0.4">
@@ -15383,7 +15384,7 @@
         <v>7</v>
       </c>
       <c r="L338" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="339" spans="1:12" x14ac:dyDescent="0.4">
@@ -15421,7 +15422,7 @@
         <v>7</v>
       </c>
       <c r="L339" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="340" spans="1:12" x14ac:dyDescent="0.4">
@@ -15459,7 +15460,7 @@
         <v>7</v>
       </c>
       <c r="L340" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="341" spans="1:12" x14ac:dyDescent="0.4">
@@ -15497,7 +15498,7 @@
         <v>7</v>
       </c>
       <c r="L341" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="342" spans="1:12" x14ac:dyDescent="0.4">
@@ -15535,7 +15536,7 @@
         <v>7</v>
       </c>
       <c r="L342" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="343" spans="1:12" x14ac:dyDescent="0.4">
@@ -15573,7 +15574,7 @@
         <v>1</v>
       </c>
       <c r="L343" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="344" spans="1:12" x14ac:dyDescent="0.4">
@@ -15611,7 +15612,7 @@
         <v>1</v>
       </c>
       <c r="L344" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="345" spans="1:12" x14ac:dyDescent="0.4">
@@ -15649,7 +15650,7 @@
         <v>1</v>
       </c>
       <c r="L345" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="346" spans="1:12" x14ac:dyDescent="0.4">
@@ -15687,7 +15688,7 @@
         <v>1</v>
       </c>
       <c r="L346" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="347" spans="1:12" x14ac:dyDescent="0.4">
@@ -15725,7 +15726,7 @@
         <v>5</v>
       </c>
       <c r="L347" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="348" spans="1:12" x14ac:dyDescent="0.4">
@@ -15763,7 +15764,7 @@
         <v>5</v>
       </c>
       <c r="L348" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="349" spans="1:12" x14ac:dyDescent="0.4">
@@ -15801,7 +15802,7 @@
         <v>3</v>
       </c>
       <c r="L349" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="350" spans="1:12" x14ac:dyDescent="0.4">
@@ -15829,7 +15830,7 @@
       <c r="J350" s="2"/>
       <c r="K350" s="2"/>
       <c r="L350" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="351" spans="1:12" x14ac:dyDescent="0.4">
@@ -15867,7 +15868,7 @@
         <v>4</v>
       </c>
       <c r="L351" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="352" spans="1:12" x14ac:dyDescent="0.4">
@@ -15905,7 +15906,7 @@
         <v>8</v>
       </c>
       <c r="L352" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="353" spans="1:12" x14ac:dyDescent="0.4">
@@ -15943,7 +15944,7 @@
         <v>8</v>
       </c>
       <c r="L353" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="354" spans="1:12" x14ac:dyDescent="0.4">
@@ -15981,7 +15982,7 @@
         <v>9</v>
       </c>
       <c r="L354" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="355" spans="1:12" x14ac:dyDescent="0.4">
@@ -16019,7 +16020,7 @@
         <v>9</v>
       </c>
       <c r="L355" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="356" spans="1:12" x14ac:dyDescent="0.4">
@@ -16047,7 +16048,7 @@
       <c r="J356" s="2"/>
       <c r="K356" s="2"/>
       <c r="L356" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="357" spans="1:12" x14ac:dyDescent="0.4">
@@ -16075,7 +16076,7 @@
       <c r="J357" s="2"/>
       <c r="K357" s="2"/>
       <c r="L357" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="358" spans="1:12" x14ac:dyDescent="0.4">
@@ -16113,7 +16114,7 @@
         <v>4</v>
       </c>
       <c r="L358" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="359" spans="1:12" x14ac:dyDescent="0.4">
@@ -16151,7 +16152,7 @@
         <v>7</v>
       </c>
       <c r="L359" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="360" spans="1:12" x14ac:dyDescent="0.4">
@@ -16189,7 +16190,7 @@
         <v>7</v>
       </c>
       <c r="L360" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="361" spans="1:12" x14ac:dyDescent="0.4">
@@ -16227,7 +16228,7 @@
         <v>4</v>
       </c>
       <c r="L361" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="362" spans="1:12" x14ac:dyDescent="0.4">
@@ -16265,7 +16266,7 @@
         <v>4</v>
       </c>
       <c r="L362" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="363" spans="1:12" x14ac:dyDescent="0.4">
@@ -16303,7 +16304,7 @@
         <v>7</v>
       </c>
       <c r="L363" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="364" spans="1:12" x14ac:dyDescent="0.4">
@@ -16341,7 +16342,7 @@
         <v>7</v>
       </c>
       <c r="L364" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="365" spans="1:12" x14ac:dyDescent="0.4">
@@ -16379,7 +16380,7 @@
         <v>7</v>
       </c>
       <c r="L365" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="366" spans="1:12" x14ac:dyDescent="0.4">
@@ -16417,7 +16418,7 @@
         <v>7</v>
       </c>
       <c r="L366" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="367" spans="1:12" x14ac:dyDescent="0.4">
@@ -16455,7 +16456,7 @@
         <v>7</v>
       </c>
       <c r="L367" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="368" spans="1:12" x14ac:dyDescent="0.4">
@@ -16493,7 +16494,7 @@
         <v>7</v>
       </c>
       <c r="L368" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="369" spans="1:12" x14ac:dyDescent="0.4">
@@ -16521,7 +16522,7 @@
       <c r="J369" s="2"/>
       <c r="K369" s="2"/>
       <c r="L369" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="370" spans="1:12" x14ac:dyDescent="0.4">
@@ -16549,7 +16550,7 @@
       <c r="J370" s="2"/>
       <c r="K370" s="2"/>
       <c r="L370" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="371" spans="1:12" x14ac:dyDescent="0.4">
@@ -16587,7 +16588,7 @@
         <v>6</v>
       </c>
       <c r="L371" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="372" spans="1:12" x14ac:dyDescent="0.4">
@@ -16625,7 +16626,7 @@
         <v>8</v>
       </c>
       <c r="L372" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="373" spans="1:12" x14ac:dyDescent="0.4">
@@ -16633,7 +16634,7 @@
         <v>2024</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>83</v>
@@ -16663,7 +16664,7 @@
         <v>8</v>
       </c>
       <c r="L373" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="374" spans="1:12" x14ac:dyDescent="0.4">
@@ -16701,7 +16702,7 @@
         <v>8</v>
       </c>
       <c r="L374" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="375" spans="1:12" x14ac:dyDescent="0.4">
@@ -16739,7 +16740,7 @@
         <v>7</v>
       </c>
       <c r="L375" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="376" spans="1:12" x14ac:dyDescent="0.4">
@@ -16777,7 +16778,7 @@
         <v>7</v>
       </c>
       <c r="L376" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="377" spans="1:12" x14ac:dyDescent="0.4">
@@ -16815,7 +16816,7 @@
         <v>6</v>
       </c>
       <c r="L377" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="378" spans="1:12" x14ac:dyDescent="0.4">
@@ -16853,7 +16854,7 @@
         <v>6</v>
       </c>
       <c r="L378" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="379" spans="1:12" x14ac:dyDescent="0.4">
@@ -16891,7 +16892,7 @@
         <v>6</v>
       </c>
       <c r="L379" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="380" spans="1:12" x14ac:dyDescent="0.4">
@@ -16929,7 +16930,7 @@
         <v>6</v>
       </c>
       <c r="L380" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="381" spans="1:12" x14ac:dyDescent="0.4">
@@ -16967,7 +16968,7 @@
         <v>5</v>
       </c>
       <c r="L381" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="382" spans="1:12" x14ac:dyDescent="0.4">
@@ -17005,7 +17006,7 @@
         <v>5</v>
       </c>
       <c r="L382" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="383" spans="1:12" x14ac:dyDescent="0.4">
@@ -17043,7 +17044,7 @@
         <v>4</v>
       </c>
       <c r="L383" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="384" spans="1:12" x14ac:dyDescent="0.4">
@@ -17081,7 +17082,7 @@
         <v>4</v>
       </c>
       <c r="L384" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="385" spans="1:12" x14ac:dyDescent="0.4">
@@ -17119,7 +17120,7 @@
         <v>9</v>
       </c>
       <c r="L385" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="386" spans="1:12" x14ac:dyDescent="0.4">
@@ -17157,7 +17158,7 @@
         <v>9</v>
       </c>
       <c r="L386" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="387" spans="1:12" x14ac:dyDescent="0.4">
@@ -17195,7 +17196,7 @@
         <v>9</v>
       </c>
       <c r="L387" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="388" spans="1:12" x14ac:dyDescent="0.4">
@@ -17233,7 +17234,7 @@
         <v>7</v>
       </c>
       <c r="L388" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="389" spans="1:12" x14ac:dyDescent="0.4">
@@ -17271,7 +17272,7 @@
         <v>7</v>
       </c>
       <c r="L389" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="390" spans="1:12" x14ac:dyDescent="0.4">
@@ -17309,7 +17310,7 @@
         <v>5</v>
       </c>
       <c r="L390" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="391" spans="1:12" x14ac:dyDescent="0.4">
@@ -17337,7 +17338,7 @@
       <c r="J391" s="2"/>
       <c r="K391" s="2"/>
       <c r="L391" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="392" spans="1:12" x14ac:dyDescent="0.4">
@@ -17365,7 +17366,7 @@
       <c r="J392" s="2"/>
       <c r="K392" s="2"/>
       <c r="L392" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="393" spans="1:12" x14ac:dyDescent="0.4">
@@ -17393,7 +17394,7 @@
       <c r="J393" s="2"/>
       <c r="K393" s="2"/>
       <c r="L393" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="394" spans="1:12" x14ac:dyDescent="0.4">
@@ -17431,7 +17432,7 @@
         <v>7</v>
       </c>
       <c r="L394" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="395" spans="1:12" x14ac:dyDescent="0.4">
@@ -17459,7 +17460,7 @@
       <c r="J395" s="2"/>
       <c r="K395" s="2"/>
       <c r="L395" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="396" spans="1:12" x14ac:dyDescent="0.4">
@@ -17497,7 +17498,7 @@
         <v>8</v>
       </c>
       <c r="L396" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="397" spans="1:12" x14ac:dyDescent="0.4">
@@ -17535,7 +17536,7 @@
         <v>7</v>
       </c>
       <c r="L397" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="398" spans="1:12" x14ac:dyDescent="0.4">
@@ -17573,7 +17574,7 @@
         <v>5</v>
       </c>
       <c r="L398" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="399" spans="1:12" x14ac:dyDescent="0.4">
@@ -17611,7 +17612,7 @@
         <v>7</v>
       </c>
       <c r="L399" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="400" spans="1:12" x14ac:dyDescent="0.4">
@@ -17649,7 +17650,7 @@
         <v>7</v>
       </c>
       <c r="L400" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="401" spans="1:12" x14ac:dyDescent="0.4">
@@ -17687,7 +17688,7 @@
         <v>5</v>
       </c>
       <c r="L401" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="402" spans="1:12" x14ac:dyDescent="0.4">
@@ -17725,7 +17726,7 @@
         <v>4</v>
       </c>
       <c r="L402" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="403" spans="1:12" x14ac:dyDescent="0.4">
@@ -17763,7 +17764,7 @@
         <v>4</v>
       </c>
       <c r="L403" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="404" spans="1:12" x14ac:dyDescent="0.4">
@@ -17801,7 +17802,7 @@
         <v>4</v>
       </c>
       <c r="L404" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="405" spans="1:12" x14ac:dyDescent="0.4">
@@ -17839,7 +17840,7 @@
         <v>3</v>
       </c>
       <c r="L405" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="406" spans="1:12" x14ac:dyDescent="0.4">
@@ -17877,7 +17878,7 @@
         <v>4</v>
       </c>
       <c r="L406" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="407" spans="1:12" x14ac:dyDescent="0.4">
@@ -17911,7 +17912,7 @@
         <v>8</v>
       </c>
       <c r="L407" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="408" spans="1:12" x14ac:dyDescent="0.4">
@@ -17945,7 +17946,7 @@
         <v>8</v>
       </c>
       <c r="L408" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="409" spans="1:12" x14ac:dyDescent="0.4">
@@ -17979,7 +17980,7 @@
         <v>8</v>
       </c>
       <c r="L409" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="410" spans="1:12" x14ac:dyDescent="0.4">
@@ -18017,7 +18018,7 @@
         <v>6</v>
       </c>
       <c r="L410" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="411" spans="1:12" x14ac:dyDescent="0.4">
@@ -18055,7 +18056,7 @@
         <v>6</v>
       </c>
       <c r="L411" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="412" spans="1:12" x14ac:dyDescent="0.4">
@@ -18093,7 +18094,7 @@
         <v>6</v>
       </c>
       <c r="L412" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="413" spans="1:12" x14ac:dyDescent="0.4">
@@ -18131,7 +18132,7 @@
         <v>6</v>
       </c>
       <c r="L413" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="414" spans="1:12" x14ac:dyDescent="0.4">
@@ -18169,7 +18170,7 @@
         <v>6</v>
       </c>
       <c r="L414" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="415" spans="1:12" x14ac:dyDescent="0.4">
@@ -18207,7 +18208,7 @@
         <v>6</v>
       </c>
       <c r="L415" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="416" spans="1:12" x14ac:dyDescent="0.4">
@@ -18245,7 +18246,7 @@
         <v>7</v>
       </c>
       <c r="L416" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="417" spans="1:12" x14ac:dyDescent="0.4">
@@ -18283,7 +18284,7 @@
         <v>7</v>
       </c>
       <c r="L417" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="418" spans="1:12" x14ac:dyDescent="0.4">
@@ -18321,7 +18322,7 @@
         <v>6</v>
       </c>
       <c r="L418" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="419" spans="1:12" x14ac:dyDescent="0.4">
@@ -18359,7 +18360,7 @@
         <v>6</v>
       </c>
       <c r="L419" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="420" spans="1:12" x14ac:dyDescent="0.4">
@@ -18397,7 +18398,7 @@
         <v>6</v>
       </c>
       <c r="L420" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="421" spans="1:12" x14ac:dyDescent="0.4">
@@ -18435,7 +18436,7 @@
         <v>6</v>
       </c>
       <c r="L421" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="422" spans="1:12" x14ac:dyDescent="0.4">
@@ -18473,7 +18474,7 @@
         <v>8</v>
       </c>
       <c r="L422" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="423" spans="1:12" x14ac:dyDescent="0.4">
@@ -18511,7 +18512,7 @@
         <v>8</v>
       </c>
       <c r="L423" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="424" spans="1:12" x14ac:dyDescent="0.4">
@@ -18549,7 +18550,7 @@
         <v>8</v>
       </c>
       <c r="L424" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="425" spans="1:12" x14ac:dyDescent="0.4">
@@ -18587,7 +18588,7 @@
         <v>8</v>
       </c>
       <c r="L425" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="426" spans="1:12" x14ac:dyDescent="0.4">
@@ -18625,7 +18626,7 @@
         <v>8</v>
       </c>
       <c r="L426" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="427" spans="1:12" x14ac:dyDescent="0.4">
@@ -18663,7 +18664,7 @@
         <v>7</v>
       </c>
       <c r="L427" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="428" spans="1:12" x14ac:dyDescent="0.4">
@@ -18701,7 +18702,7 @@
         <v>5</v>
       </c>
       <c r="L428" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="429" spans="1:12" x14ac:dyDescent="0.4">
@@ -18739,7 +18740,7 @@
         <v>5</v>
       </c>
       <c r="L429" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="430" spans="1:12" x14ac:dyDescent="0.4">
@@ -18777,7 +18778,7 @@
         <v>5</v>
       </c>
       <c r="L430" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="431" spans="1:12" x14ac:dyDescent="0.4">
@@ -18813,7 +18814,7 @@
         <v>6</v>
       </c>
       <c r="L431" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="432" spans="1:12" x14ac:dyDescent="0.4">
@@ -18849,7 +18850,7 @@
         <v>6</v>
       </c>
       <c r="L432" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="433" spans="1:12" x14ac:dyDescent="0.4">
@@ -18885,7 +18886,7 @@
         <v>6</v>
       </c>
       <c r="L433" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="434" spans="1:12" x14ac:dyDescent="0.4">
@@ -18921,7 +18922,7 @@
         <v>6</v>
       </c>
       <c r="L434" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="435" spans="1:12" x14ac:dyDescent="0.4">
@@ -18957,7 +18958,7 @@
         <v>6</v>
       </c>
       <c r="L435" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="436" spans="1:12" x14ac:dyDescent="0.4">
@@ -18993,7 +18994,7 @@
         <v>6</v>
       </c>
       <c r="L436" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="437" spans="1:12" x14ac:dyDescent="0.4">
@@ -19031,7 +19032,7 @@
         <v>5</v>
       </c>
       <c r="L437" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="438" spans="1:12" x14ac:dyDescent="0.4">
@@ -19069,7 +19070,7 @@
         <v>5</v>
       </c>
       <c r="L438" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="439" spans="1:12" x14ac:dyDescent="0.4">
@@ -19107,7 +19108,7 @@
         <v>5</v>
       </c>
       <c r="L439" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="440" spans="1:12" x14ac:dyDescent="0.4">
@@ -19145,7 +19146,7 @@
         <v>8</v>
       </c>
       <c r="L440" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="441" spans="1:12" x14ac:dyDescent="0.4">
@@ -19183,7 +19184,7 @@
         <v>8</v>
       </c>
       <c r="L441" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="442" spans="1:12" x14ac:dyDescent="0.4">
@@ -19221,7 +19222,7 @@
         <v>8</v>
       </c>
       <c r="L442" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="443" spans="1:12" x14ac:dyDescent="0.4">
@@ -19259,7 +19260,7 @@
         <v>8</v>
       </c>
       <c r="L443" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="444" spans="1:12" x14ac:dyDescent="0.4">
@@ -19297,7 +19298,7 @@
         <v>8</v>
       </c>
       <c r="L444" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="445" spans="1:12" x14ac:dyDescent="0.4">
@@ -19335,7 +19336,7 @@
         <v>8</v>
       </c>
       <c r="L445" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="446" spans="1:12" x14ac:dyDescent="0.4">
@@ -19373,7 +19374,7 @@
         <v>9</v>
       </c>
       <c r="L446" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="447" spans="1:12" x14ac:dyDescent="0.4">
@@ -19411,7 +19412,7 @@
         <v>9</v>
       </c>
       <c r="L447" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="448" spans="1:12" x14ac:dyDescent="0.4">
@@ -19449,7 +19450,7 @@
         <v>9</v>
       </c>
       <c r="L448" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="449" spans="1:12" x14ac:dyDescent="0.4">
@@ -19487,7 +19488,7 @@
         <v>9</v>
       </c>
       <c r="L449" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="450" spans="1:12" x14ac:dyDescent="0.4">
@@ -19525,7 +19526,7 @@
         <v>9</v>
       </c>
       <c r="L450" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="451" spans="1:12" x14ac:dyDescent="0.4">
@@ -19563,7 +19564,7 @@
         <v>9</v>
       </c>
       <c r="L451" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="452" spans="1:12" x14ac:dyDescent="0.4">
@@ -19601,7 +19602,7 @@
         <v>9</v>
       </c>
       <c r="L452" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="453" spans="1:12" x14ac:dyDescent="0.4">
@@ -19639,7 +19640,7 @@
         <v>8</v>
       </c>
       <c r="L453" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="454" spans="1:12" x14ac:dyDescent="0.4">
@@ -19677,7 +19678,7 @@
         <v>8</v>
       </c>
       <c r="L454" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="455" spans="1:12" x14ac:dyDescent="0.4">
@@ -19715,7 +19716,7 @@
         <v>8</v>
       </c>
       <c r="L455" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="456" spans="1:12" x14ac:dyDescent="0.4">
@@ -19753,7 +19754,7 @@
         <v>8</v>
       </c>
       <c r="L456" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="457" spans="1:12" x14ac:dyDescent="0.4">
@@ -19791,7 +19792,7 @@
         <v>6</v>
       </c>
       <c r="L457" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="458" spans="1:12" x14ac:dyDescent="0.4">
@@ -19829,7 +19830,7 @@
         <v>6</v>
       </c>
       <c r="L458" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="459" spans="1:12" x14ac:dyDescent="0.4">
@@ -19867,7 +19868,7 @@
         <v>6</v>
       </c>
       <c r="L459" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="460" spans="1:12" x14ac:dyDescent="0.4">
@@ -19905,7 +19906,7 @@
         <v>5</v>
       </c>
       <c r="L460" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="461" spans="1:12" x14ac:dyDescent="0.4">
@@ -19943,7 +19944,7 @@
         <v>5</v>
       </c>
       <c r="L461" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="462" spans="1:12" x14ac:dyDescent="0.4">
@@ -19981,7 +19982,7 @@
         <v>1</v>
       </c>
       <c r="L462" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="463" spans="1:12" x14ac:dyDescent="0.4">
@@ -20019,7 +20020,7 @@
         <v>1</v>
       </c>
       <c r="L463" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="464" spans="1:12" x14ac:dyDescent="0.4">
@@ -20057,7 +20058,7 @@
         <v>1</v>
       </c>
       <c r="L464" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="465" spans="1:12" x14ac:dyDescent="0.4">
@@ -20095,7 +20096,7 @@
         <v>7</v>
       </c>
       <c r="L465" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="466" spans="1:12" x14ac:dyDescent="0.4">
@@ -20123,7 +20124,7 @@
       <c r="J466" s="2"/>
       <c r="K466" s="2"/>
       <c r="L466" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="467" spans="1:12" x14ac:dyDescent="0.4">
@@ -20151,7 +20152,7 @@
       <c r="J467" s="2"/>
       <c r="K467" s="2"/>
       <c r="L467" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="468" spans="1:12" x14ac:dyDescent="0.4">
@@ -20179,7 +20180,7 @@
       <c r="J468" s="2"/>
       <c r="K468" s="2"/>
       <c r="L468" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="469" spans="1:12" x14ac:dyDescent="0.4">
@@ -20217,7 +20218,7 @@
         <v>6</v>
       </c>
       <c r="L469" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="470" spans="1:12" x14ac:dyDescent="0.4">
@@ -20255,7 +20256,7 @@
         <v>2</v>
       </c>
       <c r="L470" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="471" spans="1:12" x14ac:dyDescent="0.4">
@@ -20283,7 +20284,7 @@
       <c r="J471" s="2"/>
       <c r="K471" s="2"/>
       <c r="L471" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="472" spans="1:12" x14ac:dyDescent="0.4">
@@ -20321,7 +20322,7 @@
         <v>6</v>
       </c>
       <c r="L472" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="473" spans="1:12" x14ac:dyDescent="0.4">
@@ -20359,7 +20360,7 @@
         <v>6</v>
       </c>
       <c r="L473" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="474" spans="1:12" x14ac:dyDescent="0.4">
@@ -20397,7 +20398,7 @@
         <v>5</v>
       </c>
       <c r="L474" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="475" spans="1:12" x14ac:dyDescent="0.4">
@@ -20435,7 +20436,7 @@
         <v>5</v>
       </c>
       <c r="L475" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="476" spans="1:12" x14ac:dyDescent="0.4">
@@ -20473,7 +20474,7 @@
         <v>5</v>
       </c>
       <c r="L476" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="477" spans="1:12" x14ac:dyDescent="0.4">
@@ -20511,7 +20512,7 @@
         <v>6</v>
       </c>
       <c r="L477" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="478" spans="1:12" x14ac:dyDescent="0.4">
@@ -20547,7 +20548,7 @@
         <v>8</v>
       </c>
       <c r="L478" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="479" spans="1:12" x14ac:dyDescent="0.4">
@@ -20583,7 +20584,7 @@
         <v>8</v>
       </c>
       <c r="L479" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="480" spans="1:12" x14ac:dyDescent="0.4">
@@ -20619,7 +20620,7 @@
         <v>8</v>
       </c>
       <c r="L480" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="481" spans="1:12" x14ac:dyDescent="0.4">
@@ -20657,7 +20658,7 @@
         <v>8</v>
       </c>
       <c r="L481" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="482" spans="1:12" x14ac:dyDescent="0.4">
@@ -20695,7 +20696,7 @@
         <v>8</v>
       </c>
       <c r="L482" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="483" spans="1:12" x14ac:dyDescent="0.4">
@@ -20733,7 +20734,7 @@
         <v>8</v>
       </c>
       <c r="L483" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="484" spans="1:12" x14ac:dyDescent="0.4">
@@ -20771,7 +20772,7 @@
         <v>6</v>
       </c>
       <c r="L484" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="485" spans="1:12" x14ac:dyDescent="0.4">
@@ -20809,7 +20810,7 @@
         <v>6</v>
       </c>
       <c r="L485" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="486" spans="1:12" x14ac:dyDescent="0.4">
@@ -20837,7 +20838,7 @@
       <c r="J486" s="2"/>
       <c r="K486" s="2"/>
       <c r="L486" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="487" spans="1:12" x14ac:dyDescent="0.4">
@@ -20875,7 +20876,7 @@
         <v>2</v>
       </c>
       <c r="L487" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="488" spans="1:12" x14ac:dyDescent="0.4">
@@ -20913,7 +20914,7 @@
         <v>2</v>
       </c>
       <c r="L488" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="489" spans="1:12" x14ac:dyDescent="0.4">
@@ -20951,7 +20952,7 @@
         <v>2</v>
       </c>
       <c r="L489" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="490" spans="1:12" x14ac:dyDescent="0.4">
@@ -20989,7 +20990,7 @@
         <v>5</v>
       </c>
       <c r="L490" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="491" spans="1:12" x14ac:dyDescent="0.4">
@@ -21027,7 +21028,7 @@
         <v>5</v>
       </c>
       <c r="L491" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="492" spans="1:12" x14ac:dyDescent="0.4">
@@ -21065,7 +21066,7 @@
         <v>7</v>
       </c>
       <c r="L492" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="493" spans="1:12" x14ac:dyDescent="0.4">
@@ -21103,7 +21104,7 @@
         <v>7</v>
       </c>
       <c r="L493" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="494" spans="1:12" x14ac:dyDescent="0.4">
@@ -21141,7 +21142,7 @@
         <v>7</v>
       </c>
       <c r="L494" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="495" spans="1:12" x14ac:dyDescent="0.4">
@@ -21179,7 +21180,7 @@
         <v>7</v>
       </c>
       <c r="L495" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="496" spans="1:12" x14ac:dyDescent="0.4">
@@ -21217,7 +21218,7 @@
         <v>7</v>
       </c>
       <c r="L496" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="497" spans="1:12" x14ac:dyDescent="0.4">
@@ -21255,7 +21256,7 @@
         <v>5</v>
       </c>
       <c r="L497" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="498" spans="1:12" x14ac:dyDescent="0.4">
@@ -21283,7 +21284,7 @@
       <c r="J498" s="1"/>
       <c r="K498" s="1"/>
       <c r="L498" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="499" spans="1:12" x14ac:dyDescent="0.4">
@@ -21321,7 +21322,7 @@
         <v>6</v>
       </c>
       <c r="L499" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="500" spans="1:12" x14ac:dyDescent="0.4">
@@ -21359,7 +21360,7 @@
         <v>6</v>
       </c>
       <c r="L500" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="501" spans="1:12" x14ac:dyDescent="0.4">
@@ -21397,7 +21398,7 @@
         <v>7</v>
       </c>
       <c r="L501" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="502" spans="1:12" x14ac:dyDescent="0.4">
@@ -21435,7 +21436,7 @@
         <v>7</v>
       </c>
       <c r="L502" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="503" spans="1:12" x14ac:dyDescent="0.4">
@@ -21473,7 +21474,7 @@
         <v>9</v>
       </c>
       <c r="L503" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="504" spans="1:12" x14ac:dyDescent="0.4">
@@ -21511,7 +21512,7 @@
         <v>5</v>
       </c>
       <c r="L504" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="505" spans="1:12" x14ac:dyDescent="0.4">
@@ -21549,7 +21550,7 @@
         <v>5</v>
       </c>
       <c r="L505" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="506" spans="1:12" x14ac:dyDescent="0.4">
@@ -21587,7 +21588,7 @@
         <v>5</v>
       </c>
       <c r="L506" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="507" spans="1:12" x14ac:dyDescent="0.4">
@@ -21615,7 +21616,7 @@
       <c r="J507" s="2"/>
       <c r="K507" s="2"/>
       <c r="L507" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="508" spans="1:12" x14ac:dyDescent="0.4">
@@ -21643,7 +21644,7 @@
       <c r="J508" s="2"/>
       <c r="K508" s="2"/>
       <c r="L508" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="509" spans="1:12" x14ac:dyDescent="0.4">
@@ -21671,7 +21672,7 @@
       <c r="J509" s="2"/>
       <c r="K509" s="2"/>
       <c r="L509" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="510" spans="1:12" x14ac:dyDescent="0.4">
@@ -21709,7 +21710,7 @@
         <v>5</v>
       </c>
       <c r="L510" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="511" spans="1:12" x14ac:dyDescent="0.4">
@@ -21717,7 +21718,7 @@
         <v>2024</v>
       </c>
       <c r="B511" s="1" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C511" s="1" t="s">
         <v>241</v>
@@ -21747,7 +21748,7 @@
         <v>5</v>
       </c>
       <c r="L511" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="512" spans="1:12" x14ac:dyDescent="0.4">
@@ -21785,7 +21786,7 @@
         <v>3</v>
       </c>
       <c r="L512" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="513" spans="1:12" x14ac:dyDescent="0.4">
@@ -21823,7 +21824,7 @@
         <v>3</v>
       </c>
       <c r="L513" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="514" spans="1:12" x14ac:dyDescent="0.4">
@@ -21851,7 +21852,7 @@
       <c r="J514" s="2"/>
       <c r="K514" s="2"/>
       <c r="L514" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="515" spans="1:12" x14ac:dyDescent="0.4">
@@ -21889,7 +21890,7 @@
         <v>9</v>
       </c>
       <c r="L515" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="516" spans="1:12" x14ac:dyDescent="0.4">
@@ -21927,7 +21928,7 @@
         <v>9</v>
       </c>
       <c r="L516" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="517" spans="1:12" x14ac:dyDescent="0.4">
@@ -21965,7 +21966,7 @@
         <v>8</v>
       </c>
       <c r="L517" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="518" spans="1:12" x14ac:dyDescent="0.4">
@@ -22003,7 +22004,7 @@
         <v>8</v>
       </c>
       <c r="L518" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="519" spans="1:12" x14ac:dyDescent="0.4">
@@ -22041,7 +22042,7 @@
         <v>7</v>
       </c>
       <c r="L519" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="520" spans="1:12" x14ac:dyDescent="0.4">
@@ -22079,7 +22080,7 @@
         <v>4</v>
       </c>
       <c r="L520" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="521" spans="1:12" x14ac:dyDescent="0.4">
@@ -22117,7 +22118,7 @@
         <v>7</v>
       </c>
       <c r="L521" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="522" spans="1:12" x14ac:dyDescent="0.4">
@@ -22155,7 +22156,7 @@
         <v>4</v>
       </c>
       <c r="L522" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="523" spans="1:12" x14ac:dyDescent="0.4">
@@ -22193,7 +22194,7 @@
         <v>8</v>
       </c>
       <c r="L523" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="524" spans="1:12" x14ac:dyDescent="0.4">
@@ -22231,7 +22232,7 @@
         <v>8</v>
       </c>
       <c r="L524" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="525" spans="1:12" x14ac:dyDescent="0.4">
@@ -22269,7 +22270,7 @@
         <v>8</v>
       </c>
       <c r="L525" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="526" spans="1:12" x14ac:dyDescent="0.4">
@@ -22307,7 +22308,7 @@
         <v>8</v>
       </c>
       <c r="L526" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="527" spans="1:12" x14ac:dyDescent="0.4">
@@ -22345,7 +22346,7 @@
         <v>8</v>
       </c>
       <c r="L527" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="528" spans="1:12" x14ac:dyDescent="0.4">
@@ -22383,7 +22384,7 @@
         <v>2</v>
       </c>
       <c r="L528" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="529" spans="1:12" x14ac:dyDescent="0.4">
@@ -22421,7 +22422,7 @@
         <v>5</v>
       </c>
       <c r="L529" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="530" spans="1:12" x14ac:dyDescent="0.4">
@@ -22459,7 +22460,7 @@
         <v>9</v>
       </c>
       <c r="L530" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="531" spans="1:12" x14ac:dyDescent="0.4">
@@ -22497,7 +22498,7 @@
         <v>9</v>
       </c>
       <c r="L531" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="532" spans="1:12" x14ac:dyDescent="0.4">
@@ -22535,7 +22536,7 @@
         <v>3</v>
       </c>
       <c r="L532" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="533" spans="1:12" x14ac:dyDescent="0.4">
@@ -22573,7 +22574,7 @@
         <v>9</v>
       </c>
       <c r="L533" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="534" spans="1:12" x14ac:dyDescent="0.4">
@@ -22611,7 +22612,7 @@
         <v>9</v>
       </c>
       <c r="L534" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="535" spans="1:12" x14ac:dyDescent="0.4">
@@ -22649,7 +22650,7 @@
         <v>9</v>
       </c>
       <c r="L535" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="536" spans="1:12" x14ac:dyDescent="0.4">
@@ -22677,7 +22678,7 @@
       <c r="J536" s="2"/>
       <c r="K536" s="2"/>
       <c r="L536" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="537" spans="1:12" x14ac:dyDescent="0.4">
@@ -22705,7 +22706,7 @@
       <c r="J537" s="2"/>
       <c r="K537" s="2"/>
       <c r="L537" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="538" spans="1:12" x14ac:dyDescent="0.4">
@@ -22743,7 +22744,7 @@
         <v>7</v>
       </c>
       <c r="L538" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="539" spans="1:12" x14ac:dyDescent="0.4">
@@ -22781,7 +22782,7 @@
         <v>7</v>
       </c>
       <c r="L539" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="540" spans="1:12" x14ac:dyDescent="0.4">
@@ -22819,7 +22820,7 @@
         <v>7</v>
       </c>
       <c r="L540" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="541" spans="1:12" x14ac:dyDescent="0.4">
@@ -22857,7 +22858,7 @@
         <v>7</v>
       </c>
       <c r="L541" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="542" spans="1:12" x14ac:dyDescent="0.4">
@@ -22895,7 +22896,7 @@
         <v>6</v>
       </c>
       <c r="L542" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="543" spans="1:12" x14ac:dyDescent="0.4">
@@ -22933,7 +22934,7 @@
         <v>8</v>
       </c>
       <c r="L543" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="544" spans="1:12" x14ac:dyDescent="0.4">
@@ -22971,7 +22972,7 @@
         <v>8</v>
       </c>
       <c r="L544" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="545" spans="1:12" x14ac:dyDescent="0.4">
@@ -23009,7 +23010,7 @@
         <v>5</v>
       </c>
       <c r="L545" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="546" spans="1:12" x14ac:dyDescent="0.4">
@@ -23047,7 +23048,7 @@
         <v>8</v>
       </c>
       <c r="L546" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="547" spans="1:12" x14ac:dyDescent="0.4">
@@ -23085,7 +23086,7 @@
         <v>8</v>
       </c>
       <c r="L547" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="548" spans="1:12" x14ac:dyDescent="0.4">
@@ -23123,7 +23124,7 @@
         <v>8</v>
       </c>
       <c r="L548" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="549" spans="1:12" x14ac:dyDescent="0.4">
@@ -23161,7 +23162,7 @@
         <v>8</v>
       </c>
       <c r="L549" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="550" spans="1:12" x14ac:dyDescent="0.4">
@@ -23199,7 +23200,7 @@
         <v>5</v>
       </c>
       <c r="L550" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="551" spans="1:12" x14ac:dyDescent="0.4">
@@ -23237,7 +23238,7 @@
         <v>5</v>
       </c>
       <c r="L551" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="552" spans="1:12" x14ac:dyDescent="0.4">
@@ -23275,7 +23276,7 @@
         <v>5</v>
       </c>
       <c r="L552" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="553" spans="1:12" x14ac:dyDescent="0.4">
@@ -23313,7 +23314,7 @@
         <v>2</v>
       </c>
       <c r="L553" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="554" spans="1:12" x14ac:dyDescent="0.4">
@@ -23351,7 +23352,7 @@
         <v>7</v>
       </c>
       <c r="L554" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="555" spans="1:12" x14ac:dyDescent="0.4">
@@ -23389,7 +23390,7 @@
         <v>2</v>
       </c>
       <c r="L555" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="556" spans="1:12" x14ac:dyDescent="0.4">
@@ -23427,7 +23428,7 @@
         <v>2</v>
       </c>
       <c r="L556" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="557" spans="1:12" x14ac:dyDescent="0.4">
@@ -23465,7 +23466,7 @@
         <v>5</v>
       </c>
       <c r="L557" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="558" spans="1:12" x14ac:dyDescent="0.4">
@@ -23503,7 +23504,7 @@
         <v>5</v>
       </c>
       <c r="L558" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="559" spans="1:12" x14ac:dyDescent="0.4">
@@ -23541,7 +23542,7 @@
         <v>5</v>
       </c>
       <c r="L559" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="560" spans="1:12" x14ac:dyDescent="0.4">
@@ -23579,7 +23580,7 @@
         <v>5</v>
       </c>
       <c r="L560" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="561" spans="1:12" x14ac:dyDescent="0.4">
@@ -23617,7 +23618,7 @@
         <v>5</v>
       </c>
       <c r="L561" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="562" spans="1:12" x14ac:dyDescent="0.4">
@@ -23655,7 +23656,7 @@
         <v>5</v>
       </c>
       <c r="L562" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="563" spans="1:12" x14ac:dyDescent="0.4">
@@ -23693,7 +23694,7 @@
         <v>4</v>
       </c>
       <c r="L563" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="564" spans="1:12" x14ac:dyDescent="0.4">
@@ -23731,7 +23732,7 @@
         <v>4</v>
       </c>
       <c r="L564" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="565" spans="1:12" x14ac:dyDescent="0.4">
@@ -23769,7 +23770,7 @@
         <v>4</v>
       </c>
       <c r="L565" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="566" spans="1:12" x14ac:dyDescent="0.4">
@@ -23807,7 +23808,7 @@
         <v>4</v>
       </c>
       <c r="L566" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="567" spans="1:12" x14ac:dyDescent="0.4">
@@ -23845,7 +23846,7 @@
         <v>8</v>
       </c>
       <c r="L567" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="568" spans="1:12" x14ac:dyDescent="0.4">
@@ -23883,7 +23884,7 @@
         <v>8</v>
       </c>
       <c r="L568" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="569" spans="1:12" x14ac:dyDescent="0.4">
@@ -23921,7 +23922,7 @@
         <v>8</v>
       </c>
       <c r="L569" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="570" spans="1:12" x14ac:dyDescent="0.4">
@@ -23949,7 +23950,7 @@
       <c r="J570" s="2"/>
       <c r="K570" s="2"/>
       <c r="L570" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="571" spans="1:12" x14ac:dyDescent="0.4">
@@ -23977,7 +23978,7 @@
       <c r="J571" s="1"/>
       <c r="K571" s="1"/>
       <c r="L571" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="572" spans="1:12" x14ac:dyDescent="0.4">
@@ -24000,7 +24001,7 @@
         <v>5.8380000000000001</v>
       </c>
       <c r="L572" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="573" spans="1:12" x14ac:dyDescent="0.4">
@@ -24023,7 +24024,7 @@
         <v>5.8380000000000001</v>
       </c>
       <c r="L573" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="574" spans="1:12" x14ac:dyDescent="0.4">
@@ -24046,7 +24047,7 @@
         <v>5.8380000000000001</v>
       </c>
       <c r="L574" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="575" spans="1:12" x14ac:dyDescent="0.4">
@@ -24069,7 +24070,7 @@
         <v>5.8380000000000001</v>
       </c>
       <c r="L575" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="576" spans="1:12" x14ac:dyDescent="0.4">
@@ -24107,7 +24108,7 @@
         <v>5</v>
       </c>
       <c r="L576" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="577" spans="1:12" x14ac:dyDescent="0.4">
@@ -24145,7 +24146,7 @@
         <v>5</v>
       </c>
       <c r="L577" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="578" spans="1:12" x14ac:dyDescent="0.4">
@@ -24183,7 +24184,7 @@
         <v>5</v>
       </c>
       <c r="L578" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="579" spans="1:12" x14ac:dyDescent="0.4">
@@ -24221,7 +24222,7 @@
         <v>7</v>
       </c>
       <c r="L579" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="580" spans="1:12" x14ac:dyDescent="0.4">
@@ -24259,7 +24260,7 @@
         <v>5</v>
       </c>
       <c r="L580" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="581" spans="1:12" x14ac:dyDescent="0.4">
@@ -24297,7 +24298,7 @@
         <v>9</v>
       </c>
       <c r="L581" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="582" spans="1:12" x14ac:dyDescent="0.4">
@@ -24335,7 +24336,7 @@
         <v>9</v>
       </c>
       <c r="L582" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="583" spans="1:12" x14ac:dyDescent="0.4">
@@ -24373,7 +24374,7 @@
         <v>9</v>
       </c>
       <c r="L583" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="584" spans="1:12" x14ac:dyDescent="0.4">
@@ -24411,7 +24412,7 @@
         <v>9</v>
       </c>
       <c r="L584" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="585" spans="1:12" x14ac:dyDescent="0.4">
@@ -24449,7 +24450,7 @@
         <v>9</v>
       </c>
       <c r="L585" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="586" spans="1:12" x14ac:dyDescent="0.4">
@@ -24487,7 +24488,7 @@
         <v>9</v>
       </c>
       <c r="L586" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="587" spans="1:12" x14ac:dyDescent="0.4">
@@ -24525,7 +24526,7 @@
         <v>9</v>
       </c>
       <c r="L587" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="588" spans="1:12" x14ac:dyDescent="0.4">
@@ -24563,7 +24564,7 @@
         <v>9</v>
       </c>
       <c r="L588" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="589" spans="1:12" x14ac:dyDescent="0.4">
@@ -24601,7 +24602,7 @@
         <v>9</v>
       </c>
       <c r="L589" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="590" spans="1:12" x14ac:dyDescent="0.4">
@@ -24639,7 +24640,7 @@
         <v>9</v>
       </c>
       <c r="L590" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="591" spans="1:12" x14ac:dyDescent="0.4">
@@ -24677,7 +24678,7 @@
         <v>9</v>
       </c>
       <c r="L591" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="592" spans="1:12" x14ac:dyDescent="0.4">
@@ -24715,7 +24716,7 @@
         <v>9</v>
       </c>
       <c r="L592" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="593" spans="1:12" x14ac:dyDescent="0.4">
@@ -24753,7 +24754,7 @@
         <v>7</v>
       </c>
       <c r="L593" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="594" spans="1:12" x14ac:dyDescent="0.4">
@@ -24791,7 +24792,7 @@
         <v>7</v>
       </c>
       <c r="L594" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="595" spans="1:12" x14ac:dyDescent="0.4">
@@ -24829,7 +24830,7 @@
         <v>7</v>
       </c>
       <c r="L595" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="596" spans="1:12" x14ac:dyDescent="0.4">
@@ -24867,7 +24868,7 @@
         <v>6</v>
       </c>
       <c r="L596" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="597" spans="1:12" x14ac:dyDescent="0.4">
@@ -24905,7 +24906,7 @@
         <v>6</v>
       </c>
       <c r="L597" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="598" spans="1:12" x14ac:dyDescent="0.4">
@@ -24943,7 +24944,7 @@
         <v>6</v>
       </c>
       <c r="L598" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="599" spans="1:12" x14ac:dyDescent="0.4">
@@ -24981,7 +24982,7 @@
         <v>6</v>
       </c>
       <c r="L599" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="600" spans="1:12" x14ac:dyDescent="0.4">
@@ -25019,7 +25020,7 @@
         <v>6</v>
       </c>
       <c r="L600" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="601" spans="1:12" x14ac:dyDescent="0.4">
@@ -25057,7 +25058,7 @@
         <v>8</v>
       </c>
       <c r="L601" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="602" spans="1:12" x14ac:dyDescent="0.4">
@@ -25095,7 +25096,7 @@
         <v>8</v>
       </c>
       <c r="L602" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="603" spans="1:12" x14ac:dyDescent="0.4">
@@ -25133,7 +25134,7 @@
         <v>8</v>
       </c>
       <c r="L603" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="604" spans="1:12" x14ac:dyDescent="0.4">
@@ -25171,7 +25172,7 @@
         <v>8</v>
       </c>
       <c r="L604" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="605" spans="1:12" x14ac:dyDescent="0.4">
@@ -25209,7 +25210,7 @@
         <v>8</v>
       </c>
       <c r="L605" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="606" spans="1:12" x14ac:dyDescent="0.4">
@@ -25247,7 +25248,7 @@
         <v>8</v>
       </c>
       <c r="L606" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="607" spans="1:12" x14ac:dyDescent="0.4">
@@ -25285,7 +25286,7 @@
         <v>8</v>
       </c>
       <c r="L607" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="608" spans="1:12" x14ac:dyDescent="0.4">
@@ -25323,7 +25324,7 @@
         <v>8</v>
       </c>
       <c r="L608" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="609" spans="1:12" x14ac:dyDescent="0.4">
@@ -25361,7 +25362,7 @@
         <v>8</v>
       </c>
       <c r="L609" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="610" spans="1:12" x14ac:dyDescent="0.4">
@@ -25399,7 +25400,7 @@
         <v>6</v>
       </c>
       <c r="L610" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="611" spans="1:12" x14ac:dyDescent="0.4">
@@ -25437,7 +25438,7 @@
         <v>6</v>
       </c>
       <c r="L611" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="612" spans="1:12" x14ac:dyDescent="0.4">
@@ -25475,7 +25476,7 @@
         <v>6</v>
       </c>
       <c r="L612" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="613" spans="1:12" x14ac:dyDescent="0.4">
@@ -25513,7 +25514,7 @@
         <v>6</v>
       </c>
       <c r="L613" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="614" spans="1:12" x14ac:dyDescent="0.4">
@@ -25551,7 +25552,7 @@
         <v>6</v>
       </c>
       <c r="L614" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="615" spans="1:12" x14ac:dyDescent="0.4">
@@ -25589,7 +25590,7 @@
         <v>6</v>
       </c>
       <c r="L615" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="616" spans="1:12" x14ac:dyDescent="0.4">
@@ -25627,7 +25628,7 @@
         <v>6</v>
       </c>
       <c r="L616" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="617" spans="1:12" x14ac:dyDescent="0.4">
@@ -25665,7 +25666,7 @@
         <v>6</v>
       </c>
       <c r="L617" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="618" spans="1:12" x14ac:dyDescent="0.4">
@@ -25703,7 +25704,7 @@
         <v>6</v>
       </c>
       <c r="L618" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="619" spans="1:12" x14ac:dyDescent="0.4">
@@ -25741,7 +25742,7 @@
         <v>5</v>
       </c>
       <c r="L619" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="620" spans="1:12" x14ac:dyDescent="0.4">
@@ -25779,7 +25780,7 @@
         <v>5</v>
       </c>
       <c r="L620" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="621" spans="1:12" x14ac:dyDescent="0.4">
@@ -25817,7 +25818,7 @@
         <v>5</v>
       </c>
       <c r="L621" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="622" spans="1:12" x14ac:dyDescent="0.4">
@@ -25855,7 +25856,7 @@
         <v>4</v>
       </c>
       <c r="L622" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="623" spans="1:12" x14ac:dyDescent="0.4">
@@ -25893,7 +25894,7 @@
         <v>4</v>
       </c>
       <c r="L623" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="624" spans="1:12" x14ac:dyDescent="0.4">
@@ -25931,7 +25932,7 @@
         <v>4</v>
       </c>
       <c r="L624" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="625" spans="1:12" x14ac:dyDescent="0.4">
@@ -25969,7 +25970,7 @@
         <v>8</v>
       </c>
       <c r="L625" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="626" spans="1:12" x14ac:dyDescent="0.4">
@@ -26007,7 +26008,7 @@
         <v>8</v>
       </c>
       <c r="L626" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="627" spans="1:12" x14ac:dyDescent="0.4">
@@ -26045,7 +26046,7 @@
         <v>8</v>
       </c>
       <c r="L627" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="628" spans="1:12" x14ac:dyDescent="0.4">
@@ -26083,7 +26084,7 @@
         <v>8</v>
       </c>
       <c r="L628" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="629" spans="1:12" x14ac:dyDescent="0.4">
@@ -26106,7 +26107,7 @@
         <v>5.5519999999999996</v>
       </c>
       <c r="L629" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="630" spans="1:12" x14ac:dyDescent="0.4">
@@ -26129,7 +26130,7 @@
         <v>5.5519999999999996</v>
       </c>
       <c r="L630" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="631" spans="1:12" x14ac:dyDescent="0.4">
@@ -26152,7 +26153,7 @@
         <v>5.5519999999999996</v>
       </c>
       <c r="L631" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="632" spans="1:12" x14ac:dyDescent="0.4">
@@ -26175,7 +26176,7 @@
         <v>5.6479999999999997</v>
       </c>
       <c r="L632" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="633" spans="1:12" x14ac:dyDescent="0.4">
@@ -26198,7 +26199,7 @@
         <v>5.6479999999999997</v>
       </c>
       <c r="L633" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="634" spans="1:12" x14ac:dyDescent="0.4">
@@ -26236,7 +26237,7 @@
         <v>4</v>
       </c>
       <c r="L634" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="635" spans="1:12" x14ac:dyDescent="0.4">
@@ -26274,7 +26275,7 @@
         <v>4</v>
       </c>
       <c r="L635" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="636" spans="1:12" x14ac:dyDescent="0.4">
@@ -26312,7 +26313,7 @@
         <v>7</v>
       </c>
       <c r="L636" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="637" spans="1:12" x14ac:dyDescent="0.4">
@@ -26350,7 +26351,7 @@
         <v>7</v>
       </c>
       <c r="L637" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="638" spans="1:12" x14ac:dyDescent="0.4">
@@ -26388,7 +26389,7 @@
         <v>7</v>
       </c>
       <c r="L638" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="639" spans="1:12" x14ac:dyDescent="0.4">
@@ -26426,7 +26427,7 @@
         <v>7</v>
       </c>
       <c r="L639" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="640" spans="1:12" x14ac:dyDescent="0.4">
@@ -26464,7 +26465,7 @@
         <v>7</v>
       </c>
       <c r="L640" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="641" spans="1:12" x14ac:dyDescent="0.4">
@@ -26502,7 +26503,7 @@
         <v>7</v>
       </c>
       <c r="L641" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="642" spans="1:12" x14ac:dyDescent="0.4">
@@ -26540,7 +26541,7 @@
         <v>4</v>
       </c>
       <c r="L642" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="643" spans="1:12" x14ac:dyDescent="0.4">
@@ -26578,7 +26579,7 @@
         <v>5</v>
       </c>
       <c r="L643" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="644" spans="1:12" x14ac:dyDescent="0.4">
@@ -26601,7 +26602,7 @@
         <v>6.6</v>
       </c>
       <c r="L644" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="645" spans="1:12" x14ac:dyDescent="0.4">
@@ -26639,7 +26640,7 @@
         <v>7</v>
       </c>
       <c r="L645" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="646" spans="1:12" x14ac:dyDescent="0.4">
@@ -26677,7 +26678,7 @@
         <v>7</v>
       </c>
       <c r="L646" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="647" spans="1:12" x14ac:dyDescent="0.4">
@@ -26715,7 +26716,7 @@
         <v>7</v>
       </c>
       <c r="L647" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="648" spans="1:12" x14ac:dyDescent="0.4">
@@ -26753,7 +26754,7 @@
         <v>7</v>
       </c>
       <c r="L648" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="649" spans="1:12" x14ac:dyDescent="0.4">
@@ -26791,7 +26792,7 @@
         <v>7</v>
       </c>
       <c r="L649" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="650" spans="1:12" x14ac:dyDescent="0.4">
@@ -26829,7 +26830,7 @@
         <v>7</v>
       </c>
       <c r="L650" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="651" spans="1:12" x14ac:dyDescent="0.4">
@@ -26867,7 +26868,7 @@
         <v>7</v>
       </c>
       <c r="L651" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="652" spans="1:12" x14ac:dyDescent="0.4">
@@ -26905,7 +26906,7 @@
         <v>7</v>
       </c>
       <c r="L652" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="653" spans="1:12" x14ac:dyDescent="0.4">
@@ -26943,7 +26944,7 @@
         <v>7</v>
       </c>
       <c r="L653" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="654" spans="1:12" x14ac:dyDescent="0.4">
@@ -26981,7 +26982,7 @@
         <v>9</v>
       </c>
       <c r="L654" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="655" spans="1:12" x14ac:dyDescent="0.4">
@@ -27019,7 +27020,7 @@
         <v>9</v>
       </c>
       <c r="L655" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="656" spans="1:12" x14ac:dyDescent="0.4">
@@ -27057,7 +27058,7 @@
         <v>9</v>
       </c>
       <c r="L656" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="657" spans="1:12" x14ac:dyDescent="0.4">
@@ -27080,7 +27081,7 @@
         <v>5.3949999999999996</v>
       </c>
       <c r="L657" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="658" spans="1:12" x14ac:dyDescent="0.4">
@@ -27103,7 +27104,7 @@
         <v>5.3949999999999996</v>
       </c>
       <c r="L658" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="659" spans="1:12" x14ac:dyDescent="0.4">
@@ -27126,7 +27127,7 @@
         <v>5.3949999999999996</v>
       </c>
       <c r="L659" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="660" spans="1:12" x14ac:dyDescent="0.4">
@@ -27149,7 +27150,7 @@
         <v>5.3949999999999996</v>
       </c>
       <c r="L660" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="661" spans="1:12" x14ac:dyDescent="0.4">
@@ -27172,7 +27173,7 @@
         <v>6.4269999999999996</v>
       </c>
       <c r="L661" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="662" spans="1:12" x14ac:dyDescent="0.4">
@@ -27195,7 +27196,7 @@
         <v>6.4269999999999996</v>
       </c>
       <c r="L662" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="663" spans="1:12" x14ac:dyDescent="0.4">
@@ -27233,7 +27234,7 @@
         <v>4</v>
       </c>
       <c r="L663" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="664" spans="1:12" x14ac:dyDescent="0.4">
@@ -27271,7 +27272,7 @@
         <v>8</v>
       </c>
       <c r="L664" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="665" spans="1:12" x14ac:dyDescent="0.4">
@@ -27309,7 +27310,7 @@
         <v>2</v>
       </c>
       <c r="L665" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="666" spans="1:12" x14ac:dyDescent="0.4">
@@ -27347,7 +27348,7 @@
         <v>2</v>
       </c>
       <c r="L666" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="667" spans="1:12" x14ac:dyDescent="0.4">
@@ -27385,7 +27386,7 @@
         <v>2</v>
       </c>
       <c r="L667" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="668" spans="1:12" x14ac:dyDescent="0.4">
@@ -27423,7 +27424,7 @@
         <v>8</v>
       </c>
       <c r="L668" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="669" spans="1:12" x14ac:dyDescent="0.4">
@@ -27461,7 +27462,7 @@
         <v>8</v>
       </c>
       <c r="L669" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="670" spans="1:12" x14ac:dyDescent="0.4">
@@ -27499,7 +27500,7 @@
         <v>4</v>
       </c>
       <c r="L670" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="671" spans="1:12" x14ac:dyDescent="0.4">
@@ -27537,7 +27538,7 @@
         <v>4</v>
       </c>
       <c r="L671" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="672" spans="1:12" x14ac:dyDescent="0.4">
@@ -27575,7 +27576,7 @@
         <v>8</v>
       </c>
       <c r="L672" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="673" spans="1:12" x14ac:dyDescent="0.4">
@@ -27613,7 +27614,7 @@
         <v>8</v>
       </c>
       <c r="L673" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="674" spans="1:12" x14ac:dyDescent="0.4">
@@ -27636,7 +27637,7 @@
         <v>8.69</v>
       </c>
       <c r="L674" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="675" spans="1:12" x14ac:dyDescent="0.4">
@@ -27674,7 +27675,7 @@
         <v>5</v>
       </c>
       <c r="L675" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="676" spans="1:12" x14ac:dyDescent="0.4">
@@ -27712,7 +27713,7 @@
         <v>5</v>
       </c>
       <c r="L676" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="677" spans="1:12" x14ac:dyDescent="0.4">
@@ -27741,7 +27742,7 @@
         <v>7</v>
       </c>
       <c r="L677" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="678" spans="1:12" x14ac:dyDescent="0.4">
@@ -27770,7 +27771,7 @@
         <v>7</v>
       </c>
       <c r="L678" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="679" spans="1:12" x14ac:dyDescent="0.4">
@@ -27799,7 +27800,7 @@
         <v>7</v>
       </c>
       <c r="L679" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="680" spans="1:12" x14ac:dyDescent="0.4">
@@ -27837,7 +27838,7 @@
         <v>7</v>
       </c>
       <c r="L680" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="681" spans="1:12" x14ac:dyDescent="0.4">
@@ -27875,7 +27876,7 @@
         <v>5</v>
       </c>
       <c r="L681" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="682" spans="1:12" x14ac:dyDescent="0.4">
@@ -27913,7 +27914,7 @@
         <v>9</v>
       </c>
       <c r="L682" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="683" spans="1:12" x14ac:dyDescent="0.4">
@@ -27951,7 +27952,7 @@
         <v>8</v>
       </c>
       <c r="L683" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="684" spans="1:12" x14ac:dyDescent="0.4">
@@ -27989,7 +27990,7 @@
         <v>8</v>
       </c>
       <c r="L684" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="685" spans="1:12" x14ac:dyDescent="0.4">
@@ -28027,7 +28028,7 @@
         <v>8</v>
       </c>
       <c r="L685" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="686" spans="1:12" x14ac:dyDescent="0.4">
@@ -28065,7 +28066,7 @@
         <v>9</v>
       </c>
       <c r="L686" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="687" spans="1:12" x14ac:dyDescent="0.4">
@@ -28103,7 +28104,7 @@
         <v>9</v>
       </c>
       <c r="L687" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="688" spans="1:12" x14ac:dyDescent="0.4">
@@ -28141,7 +28142,7 @@
         <v>7</v>
       </c>
       <c r="L688" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="689" spans="1:12" x14ac:dyDescent="0.4">
@@ -28179,7 +28180,7 @@
         <v>7</v>
       </c>
       <c r="L689" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="690" spans="1:12" x14ac:dyDescent="0.4">
@@ -28217,7 +28218,7 @@
         <v>7</v>
       </c>
       <c r="L690" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="691" spans="1:12" x14ac:dyDescent="0.4">
@@ -28255,7 +28256,7 @@
         <v>7</v>
       </c>
       <c r="L691" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="692" spans="1:12" x14ac:dyDescent="0.4">
@@ -28293,7 +28294,7 @@
         <v>7</v>
       </c>
       <c r="L692" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="693" spans="1:12" x14ac:dyDescent="0.4">
@@ -28328,7 +28329,7 @@
         <v>5</v>
       </c>
       <c r="L693" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="694" spans="1:12" x14ac:dyDescent="0.4">
@@ -28363,7 +28364,7 @@
         <v>5</v>
       </c>
       <c r="L694" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="695" spans="1:12" x14ac:dyDescent="0.4">
@@ -28398,7 +28399,7 @@
         <v>5</v>
       </c>
       <c r="L695" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="696" spans="1:12" x14ac:dyDescent="0.4">
@@ -28433,7 +28434,7 @@
         <v>5</v>
       </c>
       <c r="L696" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="697" spans="1:12" x14ac:dyDescent="0.4">
@@ -28471,7 +28472,7 @@
         <v>6</v>
       </c>
       <c r="L697" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="698" spans="1:12" x14ac:dyDescent="0.4">
@@ -28509,7 +28510,7 @@
         <v>6</v>
       </c>
       <c r="L698" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="699" spans="1:12" x14ac:dyDescent="0.4">
@@ -28547,7 +28548,7 @@
         <v>6</v>
       </c>
       <c r="L699" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="700" spans="1:12" x14ac:dyDescent="0.4">
@@ -28585,7 +28586,7 @@
         <v>6</v>
       </c>
       <c r="L700" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="701" spans="1:12" x14ac:dyDescent="0.4">
@@ -28623,7 +28624,7 @@
         <v>6</v>
       </c>
       <c r="L701" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="702" spans="1:12" x14ac:dyDescent="0.4">
@@ -28661,7 +28662,7 @@
         <v>1</v>
       </c>
       <c r="L702" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="703" spans="1:12" x14ac:dyDescent="0.4">
@@ -28699,7 +28700,7 @@
         <v>1</v>
       </c>
       <c r="L703" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="704" spans="1:12" x14ac:dyDescent="0.4">
@@ -28737,7 +28738,7 @@
         <v>1</v>
       </c>
       <c r="L704" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="705" spans="1:12" x14ac:dyDescent="0.4">
@@ -28775,7 +28776,7 @@
         <v>1</v>
       </c>
       <c r="L705" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="706" spans="1:12" x14ac:dyDescent="0.4">
@@ -28813,7 +28814,7 @@
         <v>1</v>
       </c>
       <c r="L706" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="707" spans="1:12" x14ac:dyDescent="0.4">
@@ -28851,7 +28852,7 @@
         <v>1</v>
       </c>
       <c r="L707" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="708" spans="1:12" x14ac:dyDescent="0.4">
@@ -28874,7 +28875,7 @@
         <v>4.7590000000000003</v>
       </c>
       <c r="L708" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="709" spans="1:12" x14ac:dyDescent="0.4">
@@ -28897,7 +28898,7 @@
         <v>4.7590000000000003</v>
       </c>
       <c r="L709" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="710" spans="1:12" x14ac:dyDescent="0.4">
@@ -28935,7 +28936,7 @@
         <v>5</v>
       </c>
       <c r="L710" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="711" spans="1:12" x14ac:dyDescent="0.4">
@@ -28973,7 +28974,7 @@
         <v>5</v>
       </c>
       <c r="L711" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="712" spans="1:12" x14ac:dyDescent="0.4">
@@ -29011,7 +29012,7 @@
         <v>5</v>
       </c>
       <c r="L712" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="713" spans="1:12" x14ac:dyDescent="0.4">
@@ -29049,7 +29050,7 @@
         <v>5</v>
       </c>
       <c r="L713" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="714" spans="1:12" x14ac:dyDescent="0.4">
@@ -29087,7 +29088,7 @@
         <v>8</v>
       </c>
       <c r="L714" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="715" spans="1:12" x14ac:dyDescent="0.4">
@@ -29125,7 +29126,7 @@
         <v>5</v>
       </c>
       <c r="L715" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="716" spans="1:12" x14ac:dyDescent="0.4">
@@ -29163,7 +29164,7 @@
         <v>4</v>
       </c>
       <c r="L716" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="717" spans="1:12" x14ac:dyDescent="0.4">
@@ -29201,7 +29202,7 @@
         <v>7</v>
       </c>
       <c r="L717" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="718" spans="1:12" x14ac:dyDescent="0.4">
@@ -29239,7 +29240,7 @@
         <v>7</v>
       </c>
       <c r="L718" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="719" spans="1:12" x14ac:dyDescent="0.4">
@@ -29277,7 +29278,7 @@
         <v>7</v>
       </c>
       <c r="L719" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="720" spans="1:12" x14ac:dyDescent="0.4">
@@ -29315,7 +29316,7 @@
         <v>7</v>
       </c>
       <c r="L720" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="721" spans="1:12" x14ac:dyDescent="0.4">
@@ -29353,7 +29354,7 @@
         <v>6</v>
       </c>
       <c r="L721" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="722" spans="1:12" x14ac:dyDescent="0.4">
@@ -29391,7 +29392,7 @@
         <v>6</v>
       </c>
       <c r="L722" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="723" spans="1:12" x14ac:dyDescent="0.4">
@@ -29429,7 +29430,7 @@
         <v>6</v>
       </c>
       <c r="L723" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="724" spans="1:12" x14ac:dyDescent="0.4">
@@ -29467,7 +29468,7 @@
         <v>6</v>
       </c>
       <c r="L724" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="725" spans="1:12" x14ac:dyDescent="0.4">
@@ -29505,7 +29506,7 @@
         <v>6</v>
       </c>
       <c r="L725" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="726" spans="1:12" x14ac:dyDescent="0.4">
@@ -29543,7 +29544,7 @@
         <v>6</v>
       </c>
       <c r="L726" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="727" spans="1:12" x14ac:dyDescent="0.4">
@@ -29566,7 +29567,7 @@
         <v>7.1630000000000003</v>
       </c>
       <c r="L727" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="728" spans="1:12" x14ac:dyDescent="0.4">
@@ -29604,7 +29605,7 @@
         <v>5</v>
       </c>
       <c r="L728" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="729" spans="1:12" x14ac:dyDescent="0.4">
@@ -29642,7 +29643,7 @@
         <v>5</v>
       </c>
       <c r="L729" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="730" spans="1:12" x14ac:dyDescent="0.4">
@@ -29680,7 +29681,7 @@
         <v>5</v>
       </c>
       <c r="L730" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="731" spans="1:12" x14ac:dyDescent="0.4">
@@ -29718,7 +29719,7 @@
         <v>6</v>
       </c>
       <c r="L731" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="732" spans="1:12" x14ac:dyDescent="0.4">
@@ -29756,7 +29757,7 @@
         <v>6</v>
       </c>
       <c r="L732" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="733" spans="1:12" x14ac:dyDescent="0.4">
@@ -29794,7 +29795,7 @@
         <v>4</v>
       </c>
       <c r="L733" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="734" spans="1:12" x14ac:dyDescent="0.4">
@@ -29832,7 +29833,7 @@
         <v>6</v>
       </c>
       <c r="L734" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="735" spans="1:12" x14ac:dyDescent="0.4">
@@ -29870,7 +29871,7 @@
         <v>8</v>
       </c>
       <c r="L735" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="736" spans="1:12" x14ac:dyDescent="0.4">
@@ -29908,7 +29909,7 @@
         <v>8</v>
       </c>
       <c r="L736" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="737" spans="1:12" x14ac:dyDescent="0.4">
@@ -29946,7 +29947,7 @@
         <v>6</v>
       </c>
       <c r="L737" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="738" spans="1:12" x14ac:dyDescent="0.4">
@@ -29984,7 +29985,7 @@
         <v>6</v>
       </c>
       <c r="L738" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="739" spans="1:12" x14ac:dyDescent="0.4">
@@ -30022,7 +30023,7 @@
         <v>6</v>
       </c>
       <c r="L739" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="740" spans="1:12" x14ac:dyDescent="0.4">
@@ -30060,7 +30061,7 @@
         <v>5</v>
       </c>
       <c r="L740" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="741" spans="1:12" x14ac:dyDescent="0.4">
@@ -30098,7 +30099,7 @@
         <v>5</v>
       </c>
       <c r="L741" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="742" spans="1:12" x14ac:dyDescent="0.4">
@@ -30136,7 +30137,7 @@
         <v>7</v>
       </c>
       <c r="L742" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="743" spans="1:12" x14ac:dyDescent="0.4">
@@ -30144,7 +30145,7 @@
         <v>2025</v>
       </c>
       <c r="B743" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C743" t="s">
         <v>241</v>
@@ -30174,7 +30175,7 @@
         <v>6</v>
       </c>
       <c r="L743" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="744" spans="1:12" x14ac:dyDescent="0.4">
@@ -30212,7 +30213,7 @@
         <v>6</v>
       </c>
       <c r="L744" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="745" spans="1:12" x14ac:dyDescent="0.4">
@@ -30250,7 +30251,7 @@
         <v>6</v>
       </c>
       <c r="L745" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="746" spans="1:12" x14ac:dyDescent="0.4">
@@ -30288,7 +30289,7 @@
         <v>6</v>
       </c>
       <c r="L746" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="747" spans="1:12" x14ac:dyDescent="0.4">
@@ -30326,7 +30327,7 @@
         <v>3</v>
       </c>
       <c r="L747" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="748" spans="1:12" x14ac:dyDescent="0.4">
@@ -30364,7 +30365,7 @@
         <v>3</v>
       </c>
       <c r="L748" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="749" spans="1:12" x14ac:dyDescent="0.4">
@@ -30402,7 +30403,7 @@
         <v>5</v>
       </c>
       <c r="L749" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="750" spans="1:12" x14ac:dyDescent="0.4">
@@ -30440,7 +30441,7 @@
         <v>5</v>
       </c>
       <c r="L750" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="751" spans="1:12" x14ac:dyDescent="0.4">
@@ -30463,7 +30464,7 @@
         <v>7.28</v>
       </c>
       <c r="L751" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="752" spans="1:12" x14ac:dyDescent="0.4">
@@ -30486,7 +30487,7 @@
         <v>7.28</v>
       </c>
       <c r="L752" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="753" spans="1:12" x14ac:dyDescent="0.4">
@@ -30509,7 +30510,7 @@
         <v>7.28</v>
       </c>
       <c r="L753" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="754" spans="1:12" x14ac:dyDescent="0.4">
@@ -30532,7 +30533,7 @@
         <v>7.28</v>
       </c>
       <c r="L754" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="755" spans="1:12" x14ac:dyDescent="0.4">
@@ -30555,7 +30556,7 @@
         <v>7.28</v>
       </c>
       <c r="L755" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="756" spans="1:12" x14ac:dyDescent="0.4">
@@ -30593,7 +30594,7 @@
         <v>5</v>
       </c>
       <c r="L756" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="757" spans="1:12" x14ac:dyDescent="0.4">
@@ -30631,7 +30632,7 @@
         <v>2</v>
       </c>
       <c r="L757" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="758" spans="1:12" x14ac:dyDescent="0.4">
@@ -30669,7 +30670,7 @@
         <v>2</v>
       </c>
       <c r="L758" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="759" spans="1:12" x14ac:dyDescent="0.4">
@@ -30707,7 +30708,7 @@
         <v>2</v>
       </c>
       <c r="L759" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="760" spans="1:12" x14ac:dyDescent="0.4">
@@ -30745,7 +30746,7 @@
         <v>2</v>
       </c>
       <c r="L760" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="761" spans="1:12" x14ac:dyDescent="0.4">
@@ -30783,7 +30784,7 @@
         <v>5</v>
       </c>
       <c r="L761" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="762" spans="1:12" x14ac:dyDescent="0.4">
@@ -30815,7 +30816,7 @@
         <v>8</v>
       </c>
       <c r="L762" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="763" spans="1:12" x14ac:dyDescent="0.4">
@@ -30853,7 +30854,7 @@
         <v>3</v>
       </c>
       <c r="L763" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="764" spans="1:12" x14ac:dyDescent="0.4">
@@ -30891,7 +30892,7 @@
         <v>3</v>
       </c>
       <c r="L764" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="765" spans="1:12" x14ac:dyDescent="0.4">
@@ -30929,7 +30930,7 @@
         <v>3</v>
       </c>
       <c r="L765" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="766" spans="1:12" x14ac:dyDescent="0.4">
@@ -30967,7 +30968,7 @@
         <v>8</v>
       </c>
       <c r="L766" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="767" spans="1:12" x14ac:dyDescent="0.4">
@@ -31005,7 +31006,7 @@
         <v>8</v>
       </c>
       <c r="L767" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="768" spans="1:12" x14ac:dyDescent="0.4">
@@ -31043,7 +31044,7 @@
         <v>8</v>
       </c>
       <c r="L768" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="769" spans="1:12" x14ac:dyDescent="0.4">
@@ -31078,7 +31079,7 @@
         <v>7</v>
       </c>
       <c r="L769" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="770" spans="1:12" x14ac:dyDescent="0.4">
@@ -31101,7 +31102,7 @@
         <v>7.51</v>
       </c>
       <c r="L770" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="771" spans="1:12" x14ac:dyDescent="0.4">
@@ -31124,7 +31125,7 @@
         <v>7.51</v>
       </c>
       <c r="L771" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="772" spans="1:12" x14ac:dyDescent="0.4">
@@ -31162,7 +31163,7 @@
         <v>5</v>
       </c>
       <c r="L772" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="773" spans="1:12" x14ac:dyDescent="0.4">
@@ -31200,7 +31201,7 @@
         <v>5</v>
       </c>
       <c r="L773" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="774" spans="1:12" x14ac:dyDescent="0.4">
@@ -31238,7 +31239,7 @@
         <v>5</v>
       </c>
       <c r="L774" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="775" spans="1:12" x14ac:dyDescent="0.4">
@@ -31276,7 +31277,7 @@
         <v>5</v>
       </c>
       <c r="L775" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="776" spans="1:12" x14ac:dyDescent="0.4">
@@ -31314,7 +31315,7 @@
         <v>5</v>
       </c>
       <c r="L776" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="777" spans="1:12" x14ac:dyDescent="0.4">
@@ -31352,7 +31353,7 @@
         <v>6</v>
       </c>
       <c r="L777" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="778" spans="1:12" x14ac:dyDescent="0.4">
@@ -31390,7 +31391,7 @@
         <v>6</v>
       </c>
       <c r="L778" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="779" spans="1:12" x14ac:dyDescent="0.4">
@@ -31428,7 +31429,7 @@
         <v>6</v>
       </c>
       <c r="L779" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="780" spans="1:12" x14ac:dyDescent="0.4">
@@ -31466,7 +31467,7 @@
         <v>6</v>
       </c>
       <c r="L780" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="781" spans="1:12" x14ac:dyDescent="0.4">
@@ -31504,7 +31505,7 @@
         <v>6</v>
       </c>
       <c r="L781" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="782" spans="1:12" x14ac:dyDescent="0.4">
@@ -31542,7 +31543,7 @@
         <v>6</v>
       </c>
       <c r="L782" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="783" spans="1:12" x14ac:dyDescent="0.4">
@@ -31580,7 +31581,7 @@
         <v>6</v>
       </c>
       <c r="L783" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="784" spans="1:12" x14ac:dyDescent="0.4">
@@ -31618,7 +31619,7 @@
         <v>6</v>
       </c>
       <c r="L784" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="785" spans="1:12" x14ac:dyDescent="0.4">
@@ -31656,7 +31657,7 @@
         <v>6</v>
       </c>
       <c r="L785" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="786" spans="1:12" x14ac:dyDescent="0.4">
@@ -31694,7 +31695,7 @@
         <v>6</v>
       </c>
       <c r="L786" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="787" spans="1:12" x14ac:dyDescent="0.4">
@@ -31732,7 +31733,7 @@
         <v>6</v>
       </c>
       <c r="L787" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="788" spans="1:12" x14ac:dyDescent="0.4">
@@ -31770,7 +31771,7 @@
         <v>6</v>
       </c>
       <c r="L788" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="789" spans="1:12" x14ac:dyDescent="0.4">
@@ -31808,7 +31809,7 @@
         <v>6</v>
       </c>
       <c r="L789" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="790" spans="1:12" x14ac:dyDescent="0.4">
@@ -31846,7 +31847,7 @@
         <v>7</v>
       </c>
       <c r="L790" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="791" spans="1:12" x14ac:dyDescent="0.4">
@@ -31884,7 +31885,7 @@
         <v>7</v>
       </c>
       <c r="L791" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="792" spans="1:12" x14ac:dyDescent="0.4">
@@ -31919,7 +31920,7 @@
         <v>7</v>
       </c>
       <c r="L792" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="793" spans="1:12" x14ac:dyDescent="0.4">
@@ -31954,7 +31955,7 @@
         <v>7</v>
       </c>
       <c r="L793" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="794" spans="1:12" x14ac:dyDescent="0.4">
@@ -31992,7 +31993,7 @@
         <v>5</v>
       </c>
       <c r="L794" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="795" spans="1:12" x14ac:dyDescent="0.4">
@@ -32030,7 +32031,7 @@
         <v>5</v>
       </c>
       <c r="L795" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="796" spans="1:12" x14ac:dyDescent="0.4">
@@ -32068,7 +32069,7 @@
         <v>5</v>
       </c>
       <c r="L796" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="797" spans="1:12" x14ac:dyDescent="0.4">
@@ -32106,7 +32107,7 @@
         <v>5</v>
       </c>
       <c r="L797" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="798" spans="1:12" x14ac:dyDescent="0.4">
@@ -32144,7 +32145,7 @@
         <v>7</v>
       </c>
       <c r="L798" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="799" spans="1:12" x14ac:dyDescent="0.4">
@@ -32182,7 +32183,7 @@
         <v>7</v>
       </c>
       <c r="L799" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="800" spans="1:12" x14ac:dyDescent="0.4">
@@ -32220,7 +32221,7 @@
         <v>7</v>
       </c>
       <c r="L800" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="801" spans="1:12" x14ac:dyDescent="0.4">
@@ -32258,7 +32259,7 @@
         <v>7</v>
       </c>
       <c r="L801" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="802" spans="1:12" x14ac:dyDescent="0.4">
@@ -32296,7 +32297,7 @@
         <v>7</v>
       </c>
       <c r="L802" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="803" spans="1:12" x14ac:dyDescent="0.4">
@@ -32334,7 +32335,7 @@
         <v>7</v>
       </c>
       <c r="L803" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="804" spans="1:12" x14ac:dyDescent="0.4">
@@ -32372,7 +32373,7 @@
         <v>6</v>
       </c>
       <c r="L804" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="805" spans="1:12" x14ac:dyDescent="0.4">
@@ -32410,7 +32411,7 @@
         <v>7</v>
       </c>
       <c r="L805" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="806" spans="1:12" x14ac:dyDescent="0.4">
@@ -32448,7 +32449,7 @@
         <v>7</v>
       </c>
       <c r="L806" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="807" spans="1:12" x14ac:dyDescent="0.4">
@@ -32486,7 +32487,7 @@
         <v>7</v>
       </c>
       <c r="L807" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="808" spans="1:12" x14ac:dyDescent="0.4">
@@ -32524,7 +32525,7 @@
         <v>7</v>
       </c>
       <c r="L808" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="809" spans="1:12" x14ac:dyDescent="0.4">
@@ -32562,7 +32563,7 @@
         <v>7</v>
       </c>
       <c r="L809" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="810" spans="1:12" x14ac:dyDescent="0.4">
@@ -32600,7 +32601,7 @@
         <v>7</v>
       </c>
       <c r="L810" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="811" spans="1:12" x14ac:dyDescent="0.4">
@@ -32638,7 +32639,7 @@
         <v>5</v>
       </c>
       <c r="L811" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="812" spans="1:12" x14ac:dyDescent="0.4">
@@ -32676,7 +32677,7 @@
         <v>5</v>
       </c>
       <c r="L812" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="813" spans="1:12" x14ac:dyDescent="0.4">
@@ -32699,7 +32700,7 @@
         <v>6</v>
       </c>
       <c r="L813" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="814" spans="1:12" x14ac:dyDescent="0.4">
@@ -32737,7 +32738,7 @@
         <v>6</v>
       </c>
       <c r="L814" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="815" spans="1:12" x14ac:dyDescent="0.4">
@@ -32775,7 +32776,7 @@
         <v>6</v>
       </c>
       <c r="L815" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="816" spans="1:12" x14ac:dyDescent="0.4">
@@ -32813,7 +32814,7 @@
         <v>8</v>
       </c>
       <c r="L816" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="817" spans="1:12" x14ac:dyDescent="0.4">
@@ -32851,7 +32852,7 @@
         <v>8</v>
       </c>
       <c r="L817" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="818" spans="1:12" x14ac:dyDescent="0.4">
@@ -32889,7 +32890,7 @@
         <v>6</v>
       </c>
       <c r="L818" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="819" spans="1:12" x14ac:dyDescent="0.4">
@@ -32927,7 +32928,7 @@
         <v>6</v>
       </c>
       <c r="L819" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="820" spans="1:12" x14ac:dyDescent="0.4">
@@ -32965,7 +32966,7 @@
         <v>6</v>
       </c>
       <c r="L820" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="821" spans="1:12" x14ac:dyDescent="0.4">
@@ -33003,7 +33004,7 @@
         <v>6</v>
       </c>
       <c r="L821" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="822" spans="1:12" x14ac:dyDescent="0.4">
@@ -33041,7 +33042,7 @@
         <v>6</v>
       </c>
       <c r="L822" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="823" spans="1:12" x14ac:dyDescent="0.4">
@@ -33079,7 +33080,7 @@
         <v>6</v>
       </c>
       <c r="L823" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="824" spans="1:12" x14ac:dyDescent="0.4">
@@ -33117,7 +33118,7 @@
         <v>6</v>
       </c>
       <c r="L824" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="825" spans="1:12" x14ac:dyDescent="0.4">
@@ -33155,7 +33156,7 @@
         <v>6</v>
       </c>
       <c r="L825" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="826" spans="1:12" x14ac:dyDescent="0.4">
@@ -33193,7 +33194,7 @@
         <v>6</v>
       </c>
       <c r="L826" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="827" spans="1:12" x14ac:dyDescent="0.4">
@@ -33216,7 +33217,7 @@
         <v>6.5</v>
       </c>
       <c r="L827" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="828" spans="1:12" x14ac:dyDescent="0.4">
@@ -33254,7 +33255,7 @@
         <v>4</v>
       </c>
       <c r="L828" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="829" spans="1:12" x14ac:dyDescent="0.4">
@@ -33292,7 +33293,7 @@
         <v>4</v>
       </c>
       <c r="L829" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="830" spans="1:12" x14ac:dyDescent="0.4">
@@ -33330,7 +33331,7 @@
         <v>3</v>
       </c>
       <c r="L830" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="831" spans="1:12" x14ac:dyDescent="0.4">
@@ -33368,7 +33369,7 @@
         <v>5</v>
       </c>
       <c r="L831" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="832" spans="1:12" x14ac:dyDescent="0.4">
@@ -33406,7 +33407,7 @@
         <v>5</v>
       </c>
       <c r="L832" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="833" spans="1:12" x14ac:dyDescent="0.4">
@@ -33444,7 +33445,7 @@
         <v>5</v>
       </c>
       <c r="L833" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="834" spans="1:12" x14ac:dyDescent="0.4">
@@ -33479,7 +33480,7 @@
         <v>7</v>
       </c>
       <c r="L834" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="835" spans="1:12" x14ac:dyDescent="0.4">
@@ -33514,7 +33515,7 @@
         <v>7</v>
       </c>
       <c r="L835" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="836" spans="1:12" x14ac:dyDescent="0.4">
@@ -33549,7 +33550,7 @@
         <v>7</v>
       </c>
       <c r="L836" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="837" spans="1:12" x14ac:dyDescent="0.4">
@@ -33584,7 +33585,7 @@
         <v>7</v>
       </c>
       <c r="L837" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="838" spans="1:12" x14ac:dyDescent="0.4">
@@ -33619,7 +33620,7 @@
         <v>7</v>
       </c>
       <c r="L838" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="839" spans="1:12" x14ac:dyDescent="0.4">
@@ -33654,7 +33655,7 @@
         <v>7</v>
       </c>
       <c r="L839" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="840" spans="1:12" x14ac:dyDescent="0.4">
@@ -33689,7 +33690,7 @@
         <v>6</v>
       </c>
       <c r="L840" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="841" spans="1:12" x14ac:dyDescent="0.4">
@@ -33724,7 +33725,7 @@
         <v>6</v>
       </c>
       <c r="L841" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="842" spans="1:12" x14ac:dyDescent="0.4">
@@ -33762,7 +33763,7 @@
         <v>7</v>
       </c>
       <c r="L842" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="843" spans="1:12" x14ac:dyDescent="0.4">
@@ -33800,7 +33801,7 @@
         <v>7</v>
       </c>
       <c r="L843" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="844" spans="1:12" x14ac:dyDescent="0.4">
@@ -33838,7 +33839,7 @@
         <v>6</v>
       </c>
       <c r="L844" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="845" spans="1:12" x14ac:dyDescent="0.4">
@@ -33876,7 +33877,7 @@
         <v>6</v>
       </c>
       <c r="L845" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="846" spans="1:12" x14ac:dyDescent="0.4">
@@ -33914,7 +33915,7 @@
         <v>5</v>
       </c>
       <c r="L846" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="847" spans="1:12" x14ac:dyDescent="0.4">
@@ -33952,7 +33953,7 @@
         <v>5</v>
       </c>
       <c r="L847" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="848" spans="1:12" x14ac:dyDescent="0.4">
@@ -33990,7 +33991,7 @@
         <v>7</v>
       </c>
       <c r="L848" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="849" spans="1:12" x14ac:dyDescent="0.4">
@@ -34028,7 +34029,7 @@
         <v>7</v>
       </c>
       <c r="L849" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="850" spans="1:12" x14ac:dyDescent="0.4">
@@ -34066,7 +34067,7 @@
         <v>7</v>
       </c>
       <c r="L850" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="851" spans="1:12" x14ac:dyDescent="0.4">
@@ -34104,7 +34105,7 @@
         <v>7</v>
       </c>
       <c r="L851" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="852" spans="1:12" x14ac:dyDescent="0.4">
@@ -34142,7 +34143,7 @@
         <v>8</v>
       </c>
       <c r="L852" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="853" spans="1:12" x14ac:dyDescent="0.4">
@@ -34180,7 +34181,7 @@
         <v>8</v>
       </c>
       <c r="L853" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="854" spans="1:12" x14ac:dyDescent="0.4">
@@ -34218,7 +34219,7 @@
         <v>8</v>
       </c>
       <c r="L854" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="855" spans="1:12" x14ac:dyDescent="0.4">
@@ -34253,7 +34254,7 @@
         <v>7</v>
       </c>
       <c r="L855" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="856" spans="1:12" x14ac:dyDescent="0.4">
@@ -34291,7 +34292,7 @@
         <v>5</v>
       </c>
       <c r="L856" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="857" spans="1:12" x14ac:dyDescent="0.4">
@@ -34329,7 +34330,7 @@
         <v>5</v>
       </c>
       <c r="L857" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="858" spans="1:12" x14ac:dyDescent="0.4">
@@ -34367,7 +34368,7 @@
         <v>5</v>
       </c>
       <c r="L858" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="859" spans="1:12" x14ac:dyDescent="0.4">
@@ -34405,7 +34406,7 @@
         <v>5</v>
       </c>
       <c r="L859" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="860" spans="1:12" x14ac:dyDescent="0.4">
@@ -34443,7 +34444,7 @@
         <v>5</v>
       </c>
       <c r="L860" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="861" spans="1:12" x14ac:dyDescent="0.4">
@@ -34481,7 +34482,7 @@
         <v>2</v>
       </c>
       <c r="L861" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="862" spans="1:12" x14ac:dyDescent="0.4">
@@ -34504,7 +34505,7 @@
         <v>5.6449999999999996</v>
       </c>
       <c r="L862" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="863" spans="1:12" x14ac:dyDescent="0.4">
@@ -34527,7 +34528,7 @@
         <v>5.6449999999999996</v>
       </c>
       <c r="L863" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="864" spans="1:12" x14ac:dyDescent="0.4">
@@ -34550,7 +34551,7 @@
         <v>5.6449999999999996</v>
       </c>
       <c r="L864" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="865" spans="1:12" x14ac:dyDescent="0.4">
@@ -34573,7 +34574,7 @@
         <v>5.6449999999999996</v>
       </c>
       <c r="L865" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="866" spans="1:12" x14ac:dyDescent="0.4">
@@ -34596,7 +34597,7 @@
         <v>5.6340000000000003</v>
       </c>
       <c r="L866" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="867" spans="1:12" x14ac:dyDescent="0.4">
@@ -34634,7 +34635,7 @@
         <v>7</v>
       </c>
       <c r="L867" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="868" spans="1:12" x14ac:dyDescent="0.4">
@@ -34672,7 +34673,7 @@
         <v>7</v>
       </c>
       <c r="L868" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="869" spans="1:12" x14ac:dyDescent="0.4">
@@ -34710,7 +34711,7 @@
         <v>7</v>
       </c>
       <c r="L869" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="870" spans="1:12" x14ac:dyDescent="0.4">
@@ -34748,7 +34749,7 @@
         <v>7</v>
       </c>
       <c r="L870" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="871" spans="1:12" x14ac:dyDescent="0.4">
@@ -34786,7 +34787,7 @@
         <v>5</v>
       </c>
       <c r="L871" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="872" spans="1:12" x14ac:dyDescent="0.4">
@@ -34824,7 +34825,7 @@
         <v>3</v>
       </c>
       <c r="L872" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="873" spans="1:12" x14ac:dyDescent="0.4">
@@ -34847,7 +34848,7 @@
         <v>6.1879999999999997</v>
       </c>
       <c r="L873" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="874" spans="1:12" x14ac:dyDescent="0.4">
@@ -34885,7 +34886,7 @@
         <v>4</v>
       </c>
       <c r="L874" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="875" spans="1:12" x14ac:dyDescent="0.4">
@@ -34923,7 +34924,7 @@
         <v>4</v>
       </c>
       <c r="L875" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="876" spans="1:12" x14ac:dyDescent="0.4">
@@ -34961,7 +34962,7 @@
         <v>3</v>
       </c>
       <c r="L876" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="877" spans="1:12" x14ac:dyDescent="0.4">
@@ -34999,7 +35000,7 @@
         <v>3</v>
       </c>
       <c r="L877" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="878" spans="1:12" x14ac:dyDescent="0.4">
@@ -35037,7 +35038,7 @@
         <v>6</v>
       </c>
       <c r="L878" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="879" spans="1:12" x14ac:dyDescent="0.4">
@@ -35075,7 +35076,7 @@
         <v>6</v>
       </c>
       <c r="L879" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="880" spans="1:12" x14ac:dyDescent="0.4">
@@ -35113,7 +35114,7 @@
         <v>7</v>
       </c>
       <c r="L880" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="881" spans="1:12" x14ac:dyDescent="0.4">
@@ -35151,7 +35152,7 @@
         <v>7</v>
       </c>
       <c r="L881" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="882" spans="1:12" x14ac:dyDescent="0.4">
@@ -35189,7 +35190,7 @@
         <v>7</v>
       </c>
       <c r="L882" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="883" spans="1:12" x14ac:dyDescent="0.4">
@@ -35227,7 +35228,7 @@
         <v>7</v>
       </c>
       <c r="L883" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="884" spans="1:12" x14ac:dyDescent="0.4">
@@ -35265,7 +35266,7 @@
         <v>7</v>
       </c>
       <c r="L884" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="885" spans="1:12" x14ac:dyDescent="0.4">
@@ -35303,7 +35304,7 @@
         <v>7</v>
       </c>
       <c r="L885" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="886" spans="1:12" x14ac:dyDescent="0.4">
@@ -35341,7 +35342,7 @@
         <v>7</v>
       </c>
       <c r="L886" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="887" spans="1:12" x14ac:dyDescent="0.4">
@@ -35379,7 +35380,7 @@
         <v>5</v>
       </c>
       <c r="L887" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="888" spans="1:12" x14ac:dyDescent="0.4">
@@ -35417,7 +35418,7 @@
         <v>7</v>
       </c>
       <c r="L888" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="889" spans="1:12" x14ac:dyDescent="0.4">
@@ -35440,7 +35441,7 @@
         <v>7.3330000000000002</v>
       </c>
       <c r="L889" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="890" spans="1:12" x14ac:dyDescent="0.4">
@@ -35478,7 +35479,7 @@
         <v>3</v>
       </c>
       <c r="L890" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="891" spans="1:12" x14ac:dyDescent="0.4">
@@ -35516,7 +35517,7 @@
         <v>6</v>
       </c>
       <c r="L891" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="892" spans="1:12" x14ac:dyDescent="0.4">
@@ -35554,7 +35555,7 @@
         <v>6</v>
       </c>
       <c r="L892" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="893" spans="1:12" x14ac:dyDescent="0.4">
@@ -35592,7 +35593,7 @@
         <v>7</v>
       </c>
       <c r="L893" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="894" spans="1:12" x14ac:dyDescent="0.4">
@@ -35630,7 +35631,7 @@
         <v>7</v>
       </c>
       <c r="L894" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="895" spans="1:12" x14ac:dyDescent="0.4">
@@ -35668,7 +35669,7 @@
         <v>7</v>
       </c>
       <c r="L895" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="896" spans="1:12" x14ac:dyDescent="0.4">
@@ -35706,7 +35707,7 @@
         <v>7</v>
       </c>
       <c r="L896" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="897" spans="1:12" x14ac:dyDescent="0.4">
@@ -35729,7 +35730,7 @@
         <v>7.0540000000000003</v>
       </c>
       <c r="L897" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="898" spans="1:12" x14ac:dyDescent="0.4">
@@ -35767,7 +35768,7 @@
         <v>5</v>
       </c>
       <c r="L898" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="899" spans="1:12" x14ac:dyDescent="0.4">
@@ -35805,7 +35806,7 @@
         <v>5</v>
       </c>
       <c r="L899" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="900" spans="1:12" x14ac:dyDescent="0.4">
@@ -35840,7 +35841,7 @@
         <v>5</v>
       </c>
       <c r="L900" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="901" spans="1:12" x14ac:dyDescent="0.4">
@@ -35875,7 +35876,7 @@
         <v>5</v>
       </c>
       <c r="L901" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="902" spans="1:12" x14ac:dyDescent="0.4">
@@ -35910,7 +35911,7 @@
         <v>5</v>
       </c>
       <c r="L902" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="903" spans="1:12" x14ac:dyDescent="0.4">
@@ -35945,7 +35946,7 @@
         <v>5</v>
       </c>
       <c r="L903" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="904" spans="1:12" x14ac:dyDescent="0.4">
@@ -35980,7 +35981,7 @@
         <v>5</v>
       </c>
       <c r="L904" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="905" spans="1:12" x14ac:dyDescent="0.4">
@@ -36015,7 +36016,7 @@
         <v>5</v>
       </c>
       <c r="L905" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="906" spans="1:12" x14ac:dyDescent="0.4">
@@ -36050,7 +36051,7 @@
         <v>5</v>
       </c>
       <c r="L906" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="907" spans="1:12" x14ac:dyDescent="0.4">
@@ -36085,7 +36086,7 @@
         <v>5</v>
       </c>
       <c r="L907" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="908" spans="1:12" x14ac:dyDescent="0.4">
@@ -36123,7 +36124,7 @@
         <v>5</v>
       </c>
       <c r="L908" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="909" spans="1:12" x14ac:dyDescent="0.4">
@@ -36161,7 +36162,7 @@
         <v>5</v>
       </c>
       <c r="L909" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="910" spans="1:12" x14ac:dyDescent="0.4">
@@ -36199,7 +36200,7 @@
         <v>5</v>
       </c>
       <c r="L910" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="911" spans="1:12" x14ac:dyDescent="0.4">
@@ -36237,7 +36238,7 @@
         <v>6</v>
       </c>
       <c r="L911" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="912" spans="1:12" x14ac:dyDescent="0.4">
@@ -36275,7 +36276,7 @@
         <v>6</v>
       </c>
       <c r="L912" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="913" spans="1:12" x14ac:dyDescent="0.4">
@@ -36313,7 +36314,7 @@
         <v>6</v>
       </c>
       <c r="L913" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="914" spans="1:12" x14ac:dyDescent="0.4">
@@ -36351,7 +36352,7 @@
         <v>6</v>
       </c>
       <c r="L914" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="915" spans="1:12" x14ac:dyDescent="0.4">
@@ -36374,7 +36375,7 @@
         <v>5.09</v>
       </c>
       <c r="L915" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="916" spans="1:12" x14ac:dyDescent="0.4">
@@ -36412,7 +36413,7 @@
         <v>6</v>
       </c>
       <c r="L916" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="917" spans="1:12" x14ac:dyDescent="0.4">
@@ -36450,7 +36451,7 @@
         <v>5</v>
       </c>
       <c r="L917" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="918" spans="1:12" x14ac:dyDescent="0.4">
@@ -36488,7 +36489,7 @@
         <v>5</v>
       </c>
       <c r="L918" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="919" spans="1:12" x14ac:dyDescent="0.4">
@@ -36496,7 +36497,7 @@
         <v>2025</v>
       </c>
       <c r="B919" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C919" t="s">
         <v>241</v>
@@ -36526,7 +36527,7 @@
         <v>5</v>
       </c>
       <c r="L919" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="920" spans="1:12" x14ac:dyDescent="0.4">
@@ -36534,7 +36535,7 @@
         <v>2025</v>
       </c>
       <c r="B920" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="C920" t="s">
         <v>241</v>
@@ -36564,7 +36565,7 @@
         <v>5</v>
       </c>
       <c r="L920" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="921" spans="1:12" x14ac:dyDescent="0.4">
@@ -36572,7 +36573,7 @@
         <v>2025</v>
       </c>
       <c r="B921" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="C921" t="s">
         <v>241</v>
@@ -36602,7 +36603,7 @@
         <v>5</v>
       </c>
       <c r="L921" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="922" spans="1:12" x14ac:dyDescent="0.4">
@@ -36640,7 +36641,7 @@
         <v>6</v>
       </c>
       <c r="L922" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="923" spans="1:12" x14ac:dyDescent="0.4">
@@ -36678,7 +36679,7 @@
         <v>6</v>
       </c>
       <c r="L923" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="924" spans="1:12" x14ac:dyDescent="0.4">
@@ -36716,7 +36717,7 @@
         <v>6</v>
       </c>
       <c r="L924" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="925" spans="1:12" x14ac:dyDescent="0.4">
@@ -36754,7 +36755,7 @@
         <v>4</v>
       </c>
       <c r="L925" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="926" spans="1:12" x14ac:dyDescent="0.4">
@@ -36792,7 +36793,7 @@
         <v>4</v>
       </c>
       <c r="L926" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="927" spans="1:12" x14ac:dyDescent="0.4">
@@ -36830,7 +36831,7 @@
         <v>8</v>
       </c>
       <c r="L927" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="928" spans="1:12" x14ac:dyDescent="0.4">
@@ -36868,7 +36869,7 @@
         <v>8</v>
       </c>
       <c r="L928" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="929" spans="1:12" x14ac:dyDescent="0.4">
@@ -36906,7 +36907,7 @@
         <v>8</v>
       </c>
       <c r="L929" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="930" spans="1:12" x14ac:dyDescent="0.4">
@@ -36941,7 +36942,7 @@
         <v>7</v>
       </c>
       <c r="L930" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="931" spans="1:12" x14ac:dyDescent="0.4">
@@ -36976,7 +36977,7 @@
         <v>7</v>
       </c>
       <c r="L931" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="932" spans="1:12" x14ac:dyDescent="0.4">
@@ -36999,7 +37000,7 @@
         <v>8.4809999999999999</v>
       </c>
       <c r="L932" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="933" spans="1:12" x14ac:dyDescent="0.4">
@@ -37022,7 +37023,7 @@
         <v>8.4380000000000006</v>
       </c>
       <c r="L933" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="934" spans="1:12" x14ac:dyDescent="0.4">
@@ -37060,7 +37061,7 @@
         <v>6</v>
       </c>
       <c r="L934" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="935" spans="1:12" x14ac:dyDescent="0.4">
@@ -37083,7 +37084,7 @@
         <v>7.2949999999999999</v>
       </c>
       <c r="L935" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="936" spans="1:12" x14ac:dyDescent="0.4">
@@ -37118,7 +37119,7 @@
         <v>9</v>
       </c>
       <c r="L936" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="937" spans="1:12" x14ac:dyDescent="0.4">
@@ -37156,7 +37157,7 @@
         <v>4</v>
       </c>
       <c r="L937" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="938" spans="1:12" x14ac:dyDescent="0.4">
@@ -37194,7 +37195,7 @@
         <v>5</v>
       </c>
       <c r="L938" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="939" spans="1:12" x14ac:dyDescent="0.4">
@@ -37232,7 +37233,7 @@
         <v>5</v>
       </c>
       <c r="L939" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="940" spans="1:12" x14ac:dyDescent="0.4">
@@ -37261,7 +37262,7 @@
         <v>6</v>
       </c>
       <c r="L940" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="941" spans="1:12" x14ac:dyDescent="0.4">
@@ -37290,7 +37291,7 @@
         <v>6</v>
       </c>
       <c r="L941" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="942" spans="1:12" x14ac:dyDescent="0.4">
@@ -37319,7 +37320,7 @@
         <v>6</v>
       </c>
       <c r="L942" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="943" spans="1:12" x14ac:dyDescent="0.4">
@@ -37345,7 +37346,7 @@
         <v>759</v>
       </c>
       <c r="L943" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="944" spans="1:12" x14ac:dyDescent="0.4">
@@ -37371,7 +37372,7 @@
         <v>759</v>
       </c>
       <c r="L944" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="945" spans="1:12" x14ac:dyDescent="0.4">
@@ -37397,7 +37398,7 @@
         <v>759</v>
       </c>
       <c r="L945" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="946" spans="1:12" x14ac:dyDescent="0.4">
@@ -37423,7 +37424,7 @@
         <v>759</v>
       </c>
       <c r="L946" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="947" spans="1:12" x14ac:dyDescent="0.4">
@@ -37449,7 +37450,7 @@
         <v>759</v>
       </c>
       <c r="L947" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="948" spans="1:12" x14ac:dyDescent="0.4">
@@ -37475,7 +37476,7 @@
         <v>759</v>
       </c>
       <c r="L948" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="949" spans="1:12" x14ac:dyDescent="0.4">
@@ -37501,7 +37502,7 @@
         <v>759</v>
       </c>
       <c r="L949" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="950" spans="1:12" x14ac:dyDescent="0.4">
@@ -37509,7 +37510,7 @@
         <v>2025</v>
       </c>
       <c r="B950" t="s">
-        <v>775</v>
+        <v>806</v>
       </c>
       <c r="C950" t="s">
         <v>109</v>
@@ -37527,7 +37528,7 @@
         <v>759</v>
       </c>
       <c r="L950" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="951" spans="1:12" x14ac:dyDescent="0.4">
@@ -37553,7 +37554,7 @@
         <v>759</v>
       </c>
       <c r="L951" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="952" spans="1:12" x14ac:dyDescent="0.4">
@@ -37579,7 +37580,7 @@
         <v>759</v>
       </c>
       <c r="L952" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="953" spans="1:12" x14ac:dyDescent="0.4">
@@ -37605,7 +37606,7 @@
         <v>759</v>
       </c>
       <c r="L953" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="954" spans="1:12" x14ac:dyDescent="0.4">
@@ -37631,7 +37632,7 @@
         <v>759</v>
       </c>
       <c r="L954" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="955" spans="1:12" x14ac:dyDescent="0.4">
@@ -37657,7 +37658,7 @@
         <v>759</v>
       </c>
       <c r="L955" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="956" spans="1:12" x14ac:dyDescent="0.4">
@@ -37665,7 +37666,7 @@
         <v>2025</v>
       </c>
       <c r="B956" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C956" t="s">
         <v>109</v>
@@ -37683,7 +37684,7 @@
         <v>759</v>
       </c>
       <c r="L956" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="957" spans="1:12" x14ac:dyDescent="0.4">
@@ -37709,7 +37710,7 @@
         <v>759</v>
       </c>
       <c r="L957" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="958" spans="1:12" x14ac:dyDescent="0.4">
@@ -37735,7 +37736,7 @@
         <v>759</v>
       </c>
       <c r="L958" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="959" spans="1:12" x14ac:dyDescent="0.4">
@@ -37761,7 +37762,7 @@
         <v>759</v>
       </c>
       <c r="L959" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="960" spans="1:12" x14ac:dyDescent="0.4">
@@ -37787,7 +37788,7 @@
         <v>759</v>
       </c>
       <c r="L960" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="961" spans="1:12" x14ac:dyDescent="0.4">
@@ -37795,7 +37796,7 @@
         <v>2025</v>
       </c>
       <c r="B961" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C961" t="s">
         <v>109</v>
@@ -37813,7 +37814,7 @@
         <v>759</v>
       </c>
       <c r="L961" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
   </sheetData>
